--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -751,7 +751,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1079,10 +1079,8 @@
           <t>Suman magar</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9803822103</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9803822103</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1168,10 +1166,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
@@ -1182,7 +1178,7 @@
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -628,7 +628,30 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -643,10 +666,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
@@ -671,7 +694,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -682,16 +705,29 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -705,7 +741,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -716,12 +752,12 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="27" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -734,13 +770,13 @@
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="27" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="14" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="35" customWidth="1" min="31" max="31"/>
+    <col width="45" customWidth="1" min="31" max="31"/>
     <col width="23" customWidth="1" min="32" max="32"/>
-    <col width="29" customWidth="1" min="33" max="33"/>
+    <col width="38" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="12" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -751,10 +787,10 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
-    <col width="32" customWidth="1" min="47" max="47"/>
+    <col width="36" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
     <col width="25" customWidth="1" min="49" max="49"/>
     <col width="20" customWidth="1" min="50" max="50"/>
@@ -1212,6 +1248,214 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 9:46 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>Client is asking for technical team</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349795</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Maniraj Singh Maharjan</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Maniraj Singh Maharjan</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9823765832</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 09:46:56 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>CHB9849220717</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 12:05:36 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 09:46:56 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr"/>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Pako Newroad Tamrakar Complex Near By Tamrakar Complex - Pako Newroad Tamrakar Complex Near By Tamra</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>CDB161A</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr"/>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>21h 41m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>0</v>
@@ -544,18 +544,36 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B4" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
@@ -572,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -628,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -651,7 +669,30 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>25.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>nan%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
@@ -666,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -707,7 +748,7 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
@@ -718,16 +759,29 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>2</v>
+      <c r="B5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -741,11 +795,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
@@ -787,7 +841,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1305,20 +1359,14 @@
           <t>In Progress</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr">
         <is>
           <t>Maniraj Singh Maharjan</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9823765832</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9823765832</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1390,10 +1438,8 @@
           <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
-      <c r="AH3" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH3" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI3" s="3" t="inlineStr"/>
       <c r="AJ3" s="3" t="inlineStr"/>
@@ -1408,10 +1454,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
@@ -1422,29 +1466,29 @@
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>21h 41m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
           <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>21h 41m</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV3" s="3" t="inlineStr">
-        <is>
-          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW3" s="3" t="inlineStr">
         <is>
           <t>IPTV Issue</t>
@@ -1453,6 +1497,222 @@
       <c r="AX3" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:01 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr"/>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr"/>
+      <c r="V4" s="3" t="inlineStr"/>
+      <c r="W4" s="3" t="inlineStr"/>
+      <c r="X4" s="3" t="inlineStr"/>
+      <c r="Y4" s="3" t="inlineStr"/>
+      <c r="Z4" s="3" t="inlineStr"/>
+      <c r="AA4" s="3" t="inlineStr"/>
+      <c r="AB4" s="3" t="inlineStr"/>
+      <c r="AC4" s="3" t="inlineStr"/>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AF4" s="3" t="inlineStr"/>
+      <c r="AG4" s="3" t="inlineStr"/>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr"/>
+      <c r="AM4" s="3" t="inlineStr"/>
+      <c r="AN4" s="3" t="inlineStr"/>
+      <c r="AO4" s="3" t="inlineStr"/>
+      <c r="AP4" s="3" t="inlineStr"/>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 9:57 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr"/>
+      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AC5" s="3" t="inlineStr"/>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -550,32 +550,50 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="B5" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -646,7 +664,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -657,19 +675,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -707,12 +725,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -728,6 +748,16 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Grand Total</t>
         </is>
       </c>
@@ -741,7 +771,13 @@
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -754,34 +790,90 @@
       <c r="B3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="E4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>3</v>
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -795,7 +887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -825,23 +917,23 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="27" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="14" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="23" customWidth="1" min="32" max="32"/>
-    <col width="38" customWidth="1" min="33" max="33"/>
+    <col width="25" customWidth="1" min="32" max="32"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="18" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -1716,6 +1808,654 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:27 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>sign in issue</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350187</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Manisha Thapa</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Manisha Thapa</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9841418112</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:27:10 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9841418112</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:59:56 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:27:10 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.743545</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Thapa Complex,P8RM+QM5, Bashundhara Ring Rd Track S, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>tmanisha4271@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>05:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>2,13</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.33514</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>19h 27m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:19 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342919</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Mission shrestha</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Mission shrestha</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9840344764</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:03:48 PM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9880368739</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 06:54:03 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:19:09 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.69903</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Near Dahachok, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>9880368739@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>03:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>1,7</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.24414</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>6d 14h 15m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>6d 15h 25m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:18 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342919</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Mission shrestha</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Mission shrestha</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9840344764</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 08:03:48 PM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>9880368739</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 06:54:03 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:19:09 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t>27.69903</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>Near Dahachok, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>9880368739@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr"/>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>03:24 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Anusha Adhikari</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>1,7</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr">
+        <is>
+          <t>85.24414</t>
+        </is>
+      </c>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>6d 14h 15m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>6d 15h 25m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,50 +528,50 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Chandramani Tharu</t>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Giri</t>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -580,20 +580,56 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>42.9%</t>
+      <c r="B7" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -652,19 +688,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -687,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -698,19 +734,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>nan%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -725,14 +761,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -743,20 +781,30 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -765,87 +813,111 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="6" t="n">
-        <v>1</v>
+      <c r="G2" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -853,27 +925,64 @@
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="D8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="E8" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="4" t="n">
-        <v>5</v>
+      <c r="F8" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -887,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX8"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1875,10 +1984,8 @@
           <t>Manisha Thapa</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9841418112</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9841418112</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1913,10 +2020,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.743545</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.743545</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -1972,25 +2077,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>2,13</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.33514</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.33514</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : sign in issue  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -2091,10 +2192,8 @@
           <t>Mission shrestha</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9840344764</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9840344764</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2129,10 +2228,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.69903</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.69903</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -2188,25 +2285,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>1,7</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.24414</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.24414</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
@@ -2307,10 +2400,8 @@
           <t>Mission shrestha</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9840344764</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9840344764</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2345,10 +2436,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t>27.69903</t>
-        </is>
+      <c r="Y8" s="3" t="n">
+        <v>27.69903</v>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
@@ -2404,55 +2493,483 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
           <t>1,7</t>
         </is>
       </c>
-      <c r="AP8" s="3" t="inlineStr">
-        <is>
-          <t>85.24414</t>
-        </is>
+      <c r="AP8" s="3" t="n">
+        <v>85.24414</v>
       </c>
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>6d 14h 15m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>6d 15h 25m</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
           <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS8" s="3" t="inlineStr">
-        <is>
-          <t>6d 14h 15m</t>
-        </is>
-      </c>
-      <c r="AT8" s="3" t="inlineStr">
-        <is>
-          <t>6d 15h 25m</t>
-        </is>
-      </c>
-      <c r="AU8" s="3" t="inlineStr">
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:37 AM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>frequent slow internet</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350306</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>Dipak Rai</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>Dipak Rai</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9818698257</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:37:35 AM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>9851147880</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 03:56:44 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:37:35 AM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t>27.73288</t>
+        </is>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>Near Kapan police station ,Budhanilkantha 44600, Nepal, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>dipakrai057@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr"/>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>04:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Rita Singh</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L9-6</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>85.35932</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>18h 40m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:32 AM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349298</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>RAJENDRA BAJRACHARYA</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>RAJENDRA BAJRACHARYA</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9869562347</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 07:25:28 AM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9851077389</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 07:25:28 AM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:32:50 AM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.69838</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu KALIMATI kalimati ganesh man singh path, , ,</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>rojanbajr@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>10:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.299</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 7m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 7m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
         <is>
           <t>Completed (Closed)</t>
         </is>
       </c>
-      <c r="AV8" s="3" t="inlineStr">
-        <is>
-          <t>Case : iptv issue   has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW8" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX8" s="3" t="inlineStr">
-        <is>
-          <t>Sunil Chaudhary</t>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -568,10 +568,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -838,17 +838,17 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -888,14 +888,14 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -973,7 +973,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>1</v>
@@ -982,7 +982,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX10"/>
+  <dimension ref="A1:AX12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2608,10 +2608,8 @@
           <t>Dipak Rai</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9818698257</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9818698257</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2646,10 +2644,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t>27.73288</t>
-        </is>
+      <c r="Y9" s="3" t="n">
+        <v>27.73288</v>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
@@ -2705,25 +2701,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
           <t>L9-6</t>
         </is>
       </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>85.35932</t>
-        </is>
+      <c r="AP9" s="3" t="n">
+        <v>85.35932</v>
       </c>
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>Case : frequent slow internet   has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
@@ -2824,10 +2816,8 @@
           <t>RAJENDRA BAJRACHARYA</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9869562347</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9869562347</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2862,10 +2852,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.69838</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.69838</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2921,47 +2909,43 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.299</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.29900000000001</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 7m</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 7m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS10" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 7m</t>
-        </is>
-      </c>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>1d 3h 7m</t>
-        </is>
-      </c>
-      <c r="AU10" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV10" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW10" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -2970,6 +2954,326 @@
       <c r="AX10" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:51 AM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr"/>
+      <c r="V11" s="3" t="inlineStr"/>
+      <c r="W11" s="3" t="inlineStr"/>
+      <c r="X11" s="3" t="inlineStr"/>
+      <c r="Y11" s="3" t="inlineStr"/>
+      <c r="Z11" s="3" t="inlineStr"/>
+      <c r="AA11" s="3" t="inlineStr"/>
+      <c r="AB11" s="3" t="inlineStr"/>
+      <c r="AC11" s="3" t="inlineStr"/>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AF11" s="3" t="inlineStr"/>
+      <c r="AG11" s="3" t="inlineStr"/>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr"/>
+      <c r="AM11" s="3" t="inlineStr"/>
+      <c r="AN11" s="3" t="inlineStr"/>
+      <c r="AO11" s="3" t="inlineStr"/>
+      <c r="AP11" s="3" t="inlineStr"/>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349403</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Chausara Rai</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Chausara Rai</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9849445856</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:00:23 AM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9849445856</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 08:53:58 AM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:00:32 AM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.73813</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Near Seven Summit Treks Pvt. Ltd., Kapan, Budhanilkantha-11, Kathmandu, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr"/>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>11:00 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L18-4</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.35905</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 6m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>6</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>15.4%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>30.8%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>15.4%</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX12"/>
+  <dimension ref="A1:AX14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1042,7 +1042,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3132,10 +3132,8 @@
           <t>Chausara Rai</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9849445856</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9849445856</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3170,10 +3168,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.73813</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.73813</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -3225,47 +3221,43 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L18-4</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.35905</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.35905</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 6m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>1d 2h 6m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -3274,6 +3266,222 @@
       <c r="AX12" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:16 AM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr"/>
+      <c r="J13" s="3" t="inlineStr"/>
+      <c r="K13" s="3" t="inlineStr"/>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr"/>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr"/>
+      <c r="V13" s="3" t="inlineStr"/>
+      <c r="W13" s="3" t="inlineStr"/>
+      <c r="X13" s="3" t="inlineStr"/>
+      <c r="Y13" s="3" t="inlineStr"/>
+      <c r="Z13" s="3" t="inlineStr"/>
+      <c r="AA13" s="3" t="inlineStr"/>
+      <c r="AB13" s="3" t="inlineStr"/>
+      <c r="AC13" s="3" t="inlineStr"/>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AF13" s="3" t="inlineStr"/>
+      <c r="AG13" s="3" t="inlineStr"/>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr"/>
+      <c r="AM13" s="3" t="inlineStr"/>
+      <c r="AN13" s="3" t="inlineStr"/>
+      <c r="AO13" s="3" t="inlineStr"/>
+      <c r="AP13" s="3" t="inlineStr"/>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:03 AM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr"/>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr"/>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr"/>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr"/>
+      <c r="V14" s="3" t="inlineStr"/>
+      <c r="W14" s="3" t="inlineStr"/>
+      <c r="X14" s="3" t="inlineStr"/>
+      <c r="Y14" s="3" t="inlineStr"/>
+      <c r="Z14" s="3" t="inlineStr"/>
+      <c r="AA14" s="3" t="inlineStr"/>
+      <c r="AB14" s="3" t="inlineStr"/>
+      <c r="AC14" s="3" t="inlineStr"/>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr"/>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr"/>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr"/>
+      <c r="AM14" s="3" t="inlineStr"/>
+      <c r="AN14" s="3" t="inlineStr"/>
+      <c r="AO14" s="3" t="inlineStr"/>
+      <c r="AP14" s="3" t="inlineStr"/>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>6</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX14"/>
+  <dimension ref="A1:AX15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3485,6 +3485,114 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:23 AM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr"/>
+      <c r="J15" s="3" t="inlineStr"/>
+      <c r="K15" s="3" t="inlineStr"/>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr"/>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr"/>
+      <c r="V15" s="3" t="inlineStr"/>
+      <c r="W15" s="3" t="inlineStr"/>
+      <c r="X15" s="3" t="inlineStr"/>
+      <c r="Y15" s="3" t="inlineStr"/>
+      <c r="Z15" s="3" t="inlineStr"/>
+      <c r="AA15" s="3" t="inlineStr"/>
+      <c r="AB15" s="3" t="inlineStr"/>
+      <c r="AC15" s="3" t="inlineStr"/>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AF15" s="3" t="inlineStr"/>
+      <c r="AG15" s="3" t="inlineStr"/>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr"/>
+      <c r="AM15" s="3" t="inlineStr"/>
+      <c r="AN15" s="3" t="inlineStr"/>
+      <c r="AO15" s="3" t="inlineStr"/>
+      <c r="AP15" s="3" t="inlineStr"/>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>12.5%</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -734,10 +734,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -813,14 +813,14 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>1</v>
@@ -829,23 +829,23 @@
         <v>0</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
         <v>1</v>
@@ -967,7 +967,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>3</v>
@@ -979,10 +979,10 @@
         <v>1</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX15"/>
+  <dimension ref="A1:AX17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1030,7 +1030,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="25" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -1042,7 +1042,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -3593,6 +3593,426 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:33 AM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348307</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Dada gaun view resort</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Dada gaun view resort</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9863037399</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:36:54 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9803694263</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:36:54 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:33:43 AM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr"/>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Chundevi - Western restaurant M6WX+JC6 Chandragiri 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr"/>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>11:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>A08-CDB4</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr"/>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 56m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 56m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:43 AM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350224</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Anil Balami</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Anil Balami</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9803843277</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 03:16:57 PM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>9803843277</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 03:16:57 PM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:43:55 AM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr">
+        <is>
+          <t>27.71434</t>
+        </is>
+      </c>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>kathmandu, Swoyambhu Circle Road, near at Swoyambhu Circle Road, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>balamianil2001@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>06:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>85.28763</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>20h 26m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>20h 26m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -550,86 +550,104 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Sabin Giri</t>
+          <t>Rajesh Maharjan</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Sanjeev Giri</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Sunil Chaudhary</t>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>4</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>75.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
+      <c r="B8" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>59.1%</t>
         </is>
       </c>
     </row>
@@ -688,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>22.7%</t>
         </is>
       </c>
     </row>
@@ -711,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.3%</t>
         </is>
       </c>
     </row>
@@ -734,10 +752,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -746,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.7%</t>
         </is>
       </c>
     </row>
@@ -761,16 +779,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -791,20 +810,25 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -820,19 +844,22 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="6" t="n">
-        <v>4</v>
+      <c r="G2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -851,19 +878,22 @@
         <v>1</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G3" s="6" t="n">
-        <v>2</v>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -881,8 +911,11 @@
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="3" t="n">
         <v>1</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -906,21 +939,24 @@
       <c r="F5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
@@ -929,9 +965,12 @@
         <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -951,12 +990,15 @@
         <v>0</v>
       </c>
       <c r="E7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="G7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="6" t="n">
+      <c r="H7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
@@ -970,19 +1012,22 @@
         <v>2</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="4" t="n">
         <v>2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -996,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX17"/>
+  <dimension ref="A1:AX23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1030,13 +1075,13 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="29" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="18" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="20" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -3660,10 +3705,8 @@
           <t>Dada gaun view resort</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9863037399</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9863037399</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -3749,10 +3792,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
@@ -3763,7 +3804,7 @@
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -3864,10 +3905,8 @@
           <t>Anil Balami</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9803843277</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9803843277</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -3902,10 +3941,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y17" s="3" t="inlineStr">
-        <is>
-          <t>27.71434</t>
-        </is>
+      <c r="Y17" s="3" t="n">
+        <v>27.71434</v>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
@@ -3961,47 +3998,43 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
           <t>3,12</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>85.28763</t>
-        </is>
+      <c r="AP17" s="3" t="n">
+        <v>85.28762999999999</v>
       </c>
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>20h 26m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>20h 26m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>20h 26m</t>
-        </is>
-      </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>20h 26m</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV17" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -4010,6 +4043,1262 @@
       <c r="AX17" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:29 AM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348787</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Hari Budha</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Hari Budha</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9716119634</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 07:09:52 PM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>BKT9716119634</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 05:50:06 PM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:29:49 AM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr"/>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Radhe Radhe House - Spiritist center M8GR+RQ2 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>9716119634@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>CDB277</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr"/>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 19m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>1d 17h 39m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:25 AM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350274</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Jitendra kumar Jha</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Jitendra kumar Jha</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9860441314</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:25:30 AM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9842608686</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 03:40:48 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:25:30 AM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.68976</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>GEMS School - Higher secondary school Dhapakhel Rd, Lalitpur, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>jitendraphyhio05@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>05:45 hour</t>
+        </is>
+      </c>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Praktisha Subedi</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>CDB483</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.3443</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>19h 44m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:50 AM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350629</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Sambhu Shrestha</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Sambhu Shrestha</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9803179729</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:50:20 AM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>CHB9803179729</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 07:17:56 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:50:20 AM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>S.S. college - College Q977+VRC Budhanilkantha 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>9803179729@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>02:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>CDB532</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>16h 32m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:54 AM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>iptv not working</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347929</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Hom ghale</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Hom ghale</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9841059227</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:54:00 AM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841059227</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 09:01:25 AM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:54:00 AM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr"/>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Swayamvu dallu, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>abcdef@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>11:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>CDB255</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr"/>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 52m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:50 AM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>iptv not working</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347929</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Hom ghale</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Hom ghale</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9841059227</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:54:00 AM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>KLK9841059227</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 09:01:25 AM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:54:00 AM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr"/>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Swayamvu dallu, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr">
+        <is>
+          <t>abcdef@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>11:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>CDB255</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr"/>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 52m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:49 AM</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr"/>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349734</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>Shikhar Shrestha</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>Shikhar Shrestha</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>9849784121</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:49:02 AM</t>
+        </is>
+      </c>
+      <c r="S23" s="3" t="inlineStr"/>
+      <c r="T23" s="3" t="inlineStr"/>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>KLK9849784121</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 11:36:00 AM</t>
+        </is>
+      </c>
+      <c r="W23" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:50:46 AM</t>
+        </is>
+      </c>
+      <c r="X23" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y23" s="3" t="inlineStr"/>
+      <c r="Z23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA23" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB23" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC23" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD23" s="3" t="inlineStr"/>
+      <c r="AE23" s="3" t="inlineStr">
+        <is>
+          <t>Mount Glory English Boarding High School - High school P74X+67M Jiwan Smriti Marg Kathmandu 44600, B</t>
+        </is>
+      </c>
+      <c r="AF23" s="3" t="inlineStr">
+        <is>
+          <t>9849784121@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG23" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH23" s="3" t="inlineStr"/>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>10:14 hour</t>
+        </is>
+      </c>
+      <c r="AJ23" s="3" t="inlineStr"/>
+      <c r="AK23" s="3" t="inlineStr"/>
+      <c r="AL23" s="3" t="inlineStr">
+        <is>
+          <t>Biraj Thapa</t>
+        </is>
+      </c>
+      <c r="AM23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN23" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO23" s="3" t="inlineStr">
+        <is>
+          <t>CDB414E</t>
+        </is>
+      </c>
+      <c r="AP23" s="3" t="inlineStr"/>
+      <c r="AQ23" s="3" t="inlineStr"/>
+      <c r="AR23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 14m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX23" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>29.2%</t>
         </is>
       </c>
     </row>
@@ -856,10 +856,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -1024,10 +1024,10 @@
         <v>2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX23"/>
+  <dimension ref="A1:AX25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1075,7 +1075,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="29" customWidth="1" min="32" max="32"/>
+    <col width="31" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -4113,10 +4113,8 @@
           <t>Hari Budha</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9716119634</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9716119634</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4202,10 +4200,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
@@ -4216,7 +4212,7 @@
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4317,10 +4313,8 @@
           <t>Jitendra kumar Jha</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9860441314</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9860441314</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4355,10 +4349,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.68976</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.68976</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4414,25 +4406,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>CDB483</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.3443</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.3443</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4533,10 +4521,8 @@
           <t>Sambhu Shrestha</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9803179729</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9803179729</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4608,10 +4594,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH20" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH20" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI20" s="3" t="inlineStr">
         <is>
@@ -4630,10 +4614,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
@@ -4644,7 +4626,7 @@
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -4745,10 +4727,8 @@
           <t>Hom ghale</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9841059227</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9841059227</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -4838,10 +4818,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
@@ -4852,7 +4830,7 @@
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv not working   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -4953,10 +4931,8 @@
           <t>Hom ghale</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9841059227</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9841059227</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5046,10 +5022,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
@@ -5060,7 +5034,7 @@
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
@@ -5161,10 +5135,8 @@
           <t>Shikhar Shrestha</t>
         </is>
       </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t>9849784121</t>
-        </is>
+      <c r="O23" s="3" t="n">
+        <v>9849784121</v>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
@@ -5254,10 +5226,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN23" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN23" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO23" s="3" t="inlineStr">
         <is>
@@ -5268,29 +5238,29 @@
       <c r="AQ23" s="3" t="inlineStr"/>
       <c r="AR23" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS23" s="3" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="AT23" s="3" t="inlineStr">
+        <is>
+          <t>1d 14m</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV23" s="3" t="inlineStr">
+        <is>
           <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS23" s="3" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
-      <c r="AT23" s="3" t="inlineStr">
-        <is>
-          <t>1d 14m</t>
-        </is>
-      </c>
-      <c r="AU23" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV23" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router Upgrade  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW23" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
@@ -5299,6 +5269,438 @@
       <c r="AX23" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:05 PM</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+      <c r="H24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350135</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>Hemant Shrestha</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>Hemant Shrestha</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr">
+        <is>
+          <t>9860298562</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr"/>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:36:28 PM</t>
+        </is>
+      </c>
+      <c r="S24" s="3" t="inlineStr"/>
+      <c r="T24" s="3" t="inlineStr"/>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>9860298562</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:36:28 PM</t>
+        </is>
+      </c>
+      <c r="W24" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:05:05 PM</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y24" s="3" t="inlineStr">
+        <is>
+          <t>27.69473</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA24" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB24" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC24" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD24" s="3" t="inlineStr"/>
+      <c r="AE24" s="3" t="inlineStr">
+        <is>
+          <t>Melisa marg,Khadka Goun ,Oppoite way MK motorcycle workshop,Purano naikap,Kathmandu, Bagmati, Centra</t>
+        </is>
+      </c>
+      <c r="AF24" s="3" t="inlineStr">
+        <is>
+          <t>hemantshrestha1993@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG24" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH24" s="3" t="inlineStr"/>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>07:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ24" s="3" t="inlineStr"/>
+      <c r="AK24" s="3" t="inlineStr"/>
+      <c r="AL24" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN24" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO24" s="3" t="inlineStr">
+        <is>
+          <t>CDB592</t>
+        </is>
+      </c>
+      <c r="AP24" s="3" t="inlineStr">
+        <is>
+          <t>85.26357</t>
+        </is>
+      </c>
+      <c r="AQ24" s="3" t="inlineStr"/>
+      <c r="AR24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS24" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="AT24" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV24" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX24" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:04 PM</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350135</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>Hemant Shrestha</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>Hemant Shrestha</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>9860298562</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr"/>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:36:28 PM</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr"/>
+      <c r="T25" s="3" t="inlineStr"/>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>9860298562</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 02:36:28 PM</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:05:05 PM</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>27.69473</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA25" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB25" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC25" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD25" s="3" t="inlineStr"/>
+      <c r="AE25" s="3" t="inlineStr">
+        <is>
+          <t>Melisa marg,Khadka Goun ,Oppoite way MK motorcycle workshop,Purano naikap,Kathmandu, Bagmati, Centra</t>
+        </is>
+      </c>
+      <c r="AF25" s="3" t="inlineStr">
+        <is>
+          <t>hemantshrestha1993@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr"/>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>07:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr"/>
+      <c r="AK25" s="3" t="inlineStr"/>
+      <c r="AL25" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN25" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO25" s="3" t="inlineStr">
+        <is>
+          <t>CDB592</t>
+        </is>
+      </c>
+      <c r="AP25" s="3" t="inlineStr">
+        <is>
+          <t>85.26357</t>
+        </is>
+      </c>
+      <c r="AQ25" s="3" t="inlineStr"/>
+      <c r="AR25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW25" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX25" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>2</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>60.7%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.4%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>35.7%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -844,22 +844,22 @@
         <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
@@ -921,7 +921,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -949,7 +949,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -977,7 +977,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -1003,31 +1003,59 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" s="4" t="n">
+      <c r="C9" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="4" t="n">
+      <c r="F9" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="4" t="n">
-        <v>16</v>
+      <c r="H9" s="4" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1041,7 +1069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX25"/>
+  <dimension ref="A1:AX29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1079,10 +1107,10 @@
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
-    <col width="17" customWidth="1" min="36" max="36"/>
+    <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="19" customWidth="1" min="38" max="38"/>
-    <col width="20" customWidth="1" min="39" max="39"/>
+    <col width="21" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
@@ -5339,10 +5367,8 @@
           <t>Hemant Shrestha</t>
         </is>
       </c>
-      <c r="O24" s="3" t="inlineStr">
-        <is>
-          <t>9860298562</t>
-        </is>
+      <c r="O24" s="3" t="n">
+        <v>9860298562</v>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
@@ -5377,10 +5403,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y24" s="3" t="inlineStr">
-        <is>
-          <t>27.69473</t>
-        </is>
+      <c r="Y24" s="3" t="n">
+        <v>27.69473</v>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
@@ -5436,25 +5460,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN24" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN24" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO24" s="3" t="inlineStr">
         <is>
           <t>CDB592</t>
         </is>
       </c>
-      <c r="AP24" s="3" t="inlineStr">
-        <is>
-          <t>85.26357</t>
-        </is>
+      <c r="AP24" s="3" t="n">
+        <v>85.26357</v>
       </c>
       <c r="AQ24" s="3" t="inlineStr"/>
       <c r="AR24" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS24" s="3" t="inlineStr">
@@ -5555,10 +5575,8 @@
           <t>Hemant Shrestha</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>9860298562</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>9860298562</v>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
@@ -5593,10 +5611,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y25" s="3" t="inlineStr">
-        <is>
-          <t>27.69473</t>
-        </is>
+      <c r="Y25" s="3" t="n">
+        <v>27.69473</v>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
@@ -5652,47 +5668,43 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN25" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN25" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO25" s="3" t="inlineStr">
         <is>
           <t>CDB592</t>
         </is>
       </c>
-      <c r="AP25" s="3" t="inlineStr">
-        <is>
-          <t>85.26357</t>
-        </is>
+      <c r="AP25" s="3" t="n">
+        <v>85.26357</v>
       </c>
       <c r="AQ25" s="3" t="inlineStr"/>
       <c r="AR25" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS25" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="AT25" s="3" t="inlineStr">
+        <is>
+          <t>21h 28m</t>
+        </is>
+      </c>
+      <c r="AU25" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV25" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AS25" s="3" t="inlineStr">
-        <is>
-          <t>21h 28m</t>
-        </is>
-      </c>
-      <c r="AT25" s="3" t="inlineStr">
-        <is>
-          <t>21h 28m</t>
-        </is>
-      </c>
-      <c r="AU25" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV25" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sunil Chaudhary</t>
-        </is>
-      </c>
       <c r="AW25" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -5701,6 +5713,870 @@
       <c r="AX25" s="3" t="inlineStr">
         <is>
           <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:29 PM</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351251</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>Prabuddha Tuladhar</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>Prabuddha Tuladhar</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>9818051659</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr"/>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:29:27 PM</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr"/>
+      <c r="T26" s="3" t="inlineStr"/>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>9818051659</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 11:46:16 AM</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:29:27 PM</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t>27.706385</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA26" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB26" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC26" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD26" s="3" t="inlineStr"/>
+      <c r="AE26" s="3" t="inlineStr">
+        <is>
+          <t>Chhauni,near Bella Pre School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF26" s="3" t="inlineStr">
+        <is>
+          <t>peashun@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG26" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH26" s="3" t="inlineStr"/>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>00:43 hour</t>
+        </is>
+      </c>
+      <c r="AJ26" s="3" t="inlineStr"/>
+      <c r="AK26" s="3" t="inlineStr"/>
+      <c r="AL26" s="3" t="inlineStr">
+        <is>
+          <t>Seeta Magar</t>
+        </is>
+      </c>
+      <c r="AM26" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN26" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO26" s="3" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="AP26" s="3" t="inlineStr">
+        <is>
+          <t>85.295835</t>
+        </is>
+      </c>
+      <c r="AQ26" s="3" t="inlineStr"/>
+      <c r="AR26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS26" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT26" s="3" t="inlineStr">
+        <is>
+          <t>43m</t>
+        </is>
+      </c>
+      <c r="AU26" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV26" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW26" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX26" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:23 PM</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr"/>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348585</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>Achalshail Khadka</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>Achalshail Khadka</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>9848581014</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr"/>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:23:23 PM</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr"/>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>9848581014</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 03:36:18 PM</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:23:23 PM</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y27" s="3" t="inlineStr">
+        <is>
+          <t>27.67958</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA27" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB27" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC27" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD27" s="3" t="inlineStr"/>
+      <c r="AE27" s="3" t="inlineStr">
+        <is>
+          <t>Koteshwor Dharmasthal marg, Near Deepika School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF27" s="3" t="inlineStr">
+        <is>
+          <t>hkhadka317@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG27" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH27" s="3" t="inlineStr"/>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>12:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr"/>
+      <c r="AK27" s="3" t="inlineStr"/>
+      <c r="AL27" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN27" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO27" s="3" t="inlineStr">
+        <is>
+          <t>1,1</t>
+        </is>
+      </c>
+      <c r="AP27" s="3" t="inlineStr">
+        <is>
+          <t>85.34365</t>
+        </is>
+      </c>
+      <c r="AQ27" s="3" t="inlineStr"/>
+      <c r="AR27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS27" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT27" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 47m</t>
+        </is>
+      </c>
+      <c r="AU27" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV27" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW27" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX27" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:26 PM</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348423</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>Prem Bahadur Kunwar</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>Prem Bahadur Kunwar</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>9841458042</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr"/>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:01:08 PM</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr"/>
+      <c r="T28" s="3" t="inlineStr"/>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>9841458042</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:01:08 PM</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:26:53 PM</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y28" s="3" t="inlineStr"/>
+      <c r="Z28" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA28" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB28" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC28" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD28" s="3" t="inlineStr"/>
+      <c r="AE28" s="3" t="inlineStr">
+        <is>
+          <t>Shree Manohar Secondary School - Community school P8P9+XPM Tokha 44600, , ,</t>
+        </is>
+      </c>
+      <c r="AF28" s="3" t="inlineStr">
+        <is>
+          <t>kunwarprem849@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG28" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH28" s="3" t="inlineStr"/>
+      <c r="AI28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="3" t="inlineStr"/>
+      <c r="AK28" s="3" t="inlineStr"/>
+      <c r="AL28" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO28" s="3" t="inlineStr">
+        <is>
+          <t>L55-5</t>
+        </is>
+      </c>
+      <c r="AP28" s="3" t="inlineStr"/>
+      <c r="AQ28" s="3" t="inlineStr"/>
+      <c r="AR28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS28" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 25m</t>
+        </is>
+      </c>
+      <c r="AT28" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 25m</t>
+        </is>
+      </c>
+      <c r="AU28" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV28" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW28" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX28" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:21 PM</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349846</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>Yangu Tamang</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>Yangu Tamang</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>9840602966</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr"/>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:24:54 PM</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t>30 Sep 2026 04: 29:00 PM</t>
+        </is>
+      </c>
+      <c r="T29" s="3" t="inlineStr"/>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>9847788551</t>
+        </is>
+      </c>
+      <c r="V29" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 12:29:19 PM</t>
+        </is>
+      </c>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:25:14 PM</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y29" s="3" t="inlineStr">
+        <is>
+          <t>27.744813</t>
+        </is>
+      </c>
+      <c r="Z29" s="3" t="inlineStr">
+        <is>
+          <t>No Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA29" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB29" s="3" t="inlineStr">
+        <is>
+          <t>Hari Rijal</t>
+        </is>
+      </c>
+      <c r="AC29" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD29" s="3" t="inlineStr"/>
+      <c r="AE29" s="3" t="inlineStr">
+        <is>
+          <t>Fluorescent secondary school, Baniyatar, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF29" s="3" t="inlineStr">
+        <is>
+          <t>yangutamang5@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG29" s="3" t="inlineStr">
+        <is>
+          <t>Fiber wire breakage suspect</t>
+        </is>
+      </c>
+      <c r="AH29" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI29" s="3" t="inlineStr">
+        <is>
+          <t>10:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ29" s="3" t="inlineStr">
+        <is>
+          <t>13:57 hour / 00:00 hour</t>
+        </is>
+      </c>
+      <c r="AK29" s="3" t="inlineStr"/>
+      <c r="AL29" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM29" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AN29" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO29" s="3" t="inlineStr">
+        <is>
+          <t>3,14</t>
+        </is>
+      </c>
+      <c r="AP29" s="3" t="inlineStr">
+        <is>
+          <t>85.317203</t>
+        </is>
+      </c>
+      <c r="AQ29" s="3" t="inlineStr"/>
+      <c r="AR29" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>23h 55m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>63.3%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>5</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>23.3%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>9</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.7%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
@@ -859,7 +859,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -921,14 +921,14 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -977,14 +977,14 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -1005,7 +1005,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -1018,10 +1018,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1031,31 +1031,59 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="4" t="n">
+      <c r="B10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="4" t="n">
+      <c r="E10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G10" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>20</v>
+      <c r="H10" s="4" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1069,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX29"/>
+  <dimension ref="A1:AX31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1087,7 +1115,7 @@
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="25" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
@@ -1097,7 +1125,7 @@
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="27" customWidth="1" min="26" max="26"/>
+    <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
@@ -1109,7 +1137,7 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="26" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="19" customWidth="1" min="38" max="38"/>
+    <col width="28" customWidth="1" min="38" max="38"/>
     <col width="21" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
@@ -5783,10 +5811,8 @@
           <t>Prabuddha Tuladhar</t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>9818051659</t>
-        </is>
+      <c r="O26" s="3" t="n">
+        <v>9818051659</v>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
@@ -5821,10 +5847,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t>27.706385</t>
-        </is>
+      <c r="Y26" s="3" t="n">
+        <v>27.706385</v>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
@@ -5880,25 +5904,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN26" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN26" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO26" s="3" t="inlineStr">
         <is>
           <t>2,4</t>
         </is>
       </c>
-      <c r="AP26" s="3" t="inlineStr">
-        <is>
-          <t>85.295835</t>
-        </is>
+      <c r="AP26" s="3" t="n">
+        <v>85.295835</v>
       </c>
       <c r="AQ26" s="3" t="inlineStr"/>
       <c r="AR26" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 Router   has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS26" s="3" t="inlineStr">
@@ -5999,10 +6019,8 @@
           <t>Achalshail Khadka</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
-        <is>
-          <t>9848581014</t>
-        </is>
+      <c r="O27" s="3" t="n">
+        <v>9848581014</v>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
@@ -6037,10 +6055,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y27" s="3" t="inlineStr">
-        <is>
-          <t>27.67958</t>
-        </is>
+      <c r="Y27" s="3" t="n">
+        <v>27.67958</v>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
@@ -6096,25 +6112,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN27" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN27" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO27" s="3" t="inlineStr">
         <is>
           <t>1,1</t>
         </is>
       </c>
-      <c r="AP27" s="3" t="inlineStr">
-        <is>
-          <t>85.34365</t>
-        </is>
+      <c r="AP27" s="3" t="n">
+        <v>85.34365</v>
       </c>
       <c r="AQ27" s="3" t="inlineStr"/>
       <c r="AR27" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS27" s="3" t="inlineStr">
@@ -6215,10 +6227,8 @@
           <t>Prem Bahadur Kunwar</t>
         </is>
       </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t>9841458042</t>
-        </is>
+      <c r="O28" s="3" t="n">
+        <v>9841458042</v>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
@@ -6304,10 +6314,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN28" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO28" s="3" t="inlineStr">
         <is>
@@ -6318,7 +6326,7 @@
       <c r="AQ28" s="3" t="inlineStr"/>
       <c r="AR28" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS28" s="3" t="inlineStr">
@@ -6419,10 +6427,8 @@
           <t>Yangu Tamang</t>
         </is>
       </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>9840602966</t>
-        </is>
+      <c r="O29" s="3" t="n">
+        <v>9840602966</v>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
@@ -6461,10 +6467,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y29" s="3" t="inlineStr">
-        <is>
-          <t>27.744813</t>
-        </is>
+      <c r="Y29" s="3" t="n">
+        <v>27.744813</v>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
@@ -6502,10 +6506,8 @@
           <t>Fiber wire breakage suspect</t>
         </is>
       </c>
-      <c r="AH29" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH29" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI29" s="3" t="inlineStr">
         <is>
@@ -6528,55 +6530,463 @@
           <t>MS TICKET  HANDLER</t>
         </is>
       </c>
-      <c r="AN29" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN29" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO29" s="3" t="inlineStr">
         <is>
           <t>3,14</t>
         </is>
       </c>
-      <c r="AP29" s="3" t="inlineStr">
-        <is>
-          <t>85.317203</t>
-        </is>
+      <c r="AP29" s="3" t="n">
+        <v>85.31720300000001</v>
       </c>
       <c r="AQ29" s="3" t="inlineStr"/>
       <c r="AR29" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS29" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT29" s="3" t="inlineStr">
+        <is>
+          <t>23h 55m</t>
+        </is>
+      </c>
+      <c r="AU29" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (In Progress)</t>
+        </is>
+      </c>
+      <c r="AV29" s="3" t="inlineStr">
+        <is>
           <t>Case : no light blinking   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS29" s="3" t="inlineStr">
+      <c r="AW29" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX29" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:36 PM</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+      <c r="H30" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349429</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Bishwokarma</t>
+        </is>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Bishwokarma</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>9765209837</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr"/>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:36:23 PM</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="inlineStr"/>
+      <c r="T30" s="3" t="inlineStr"/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>CHB9765209837</t>
+        </is>
+      </c>
+      <c r="V30" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 09:14:16 AM</t>
+        </is>
+      </c>
+      <c r="W30" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:36:23 PM</t>
+        </is>
+      </c>
+      <c r="X30" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y30" s="3" t="inlineStr"/>
+      <c r="Z30" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA30" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB30" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC30" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD30" s="3" t="inlineStr"/>
+      <c r="AE30" s="3" t="inlineStr">
+        <is>
+          <t>ktm budhanilkantha jay baglug kalika sun chandi pasal, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF30" s="3" t="inlineStr">
+        <is>
+          <t>bk95@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH30" s="3" t="inlineStr"/>
+      <c r="AI30" s="3" t="inlineStr">
+        <is>
+          <t>12:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ30" s="3" t="inlineStr"/>
+      <c r="AK30" s="3" t="inlineStr"/>
+      <c r="AL30" s="3" t="inlineStr">
+        <is>
+          <t>Roshan Yadav (L1 Support)</t>
+        </is>
+      </c>
+      <c r="AM30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN30" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO30" s="3" t="inlineStr">
+        <is>
+          <t>L29-2</t>
+        </is>
+      </c>
+      <c r="AP30" s="3" t="inlineStr"/>
+      <c r="AQ30" s="3" t="inlineStr"/>
+      <c r="AR30" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS30" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT29" s="3" t="inlineStr">
-        <is>
-          <t>23h 55m</t>
-        </is>
-      </c>
-      <c r="AU29" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (In Progress)</t>
-        </is>
-      </c>
-      <c r="AV29" s="3" t="inlineStr">
-        <is>
-          <t>Case : no light blinking   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW29" s="3" t="inlineStr">
+      <c r="AT30" s="3" t="inlineStr">
+        <is>
+          <t>1d 3h 22m</t>
+        </is>
+      </c>
+      <c r="AU30" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV30" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW30" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX30" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:34 PM</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr"/>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>TKT1340727</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>Kamala gharti magar</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>Kamala gharti magar</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>9860205079</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
         <is>
           <t>General / Other Issues</t>
         </is>
       </c>
-      <c r="AX29" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="Q31" s="3" t="inlineStr"/>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:43:52 AM</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr"/>
+      <c r="T31" s="3" t="inlineStr"/>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>9860205079</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
+        <is>
+          <t>20 Sep 2026 08:53:45 PM</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:34:36 PM</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y31" s="3" t="inlineStr"/>
+      <c r="Z31" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA31" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB31" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC31" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD31" s="3" t="inlineStr"/>
+      <c r="AE31" s="3" t="inlineStr">
+        <is>
+          <t>Balaju Height Micro Station - Bus station Kathmandu 44600 - Kathmandu Metropolitan, Kathmandu, Bagma</t>
+        </is>
+      </c>
+      <c r="AF31" s="3" t="inlineStr"/>
+      <c r="AG31" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH31" s="3" t="inlineStr"/>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>00:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ31" s="3" t="inlineStr"/>
+      <c r="AK31" s="3" t="inlineStr"/>
+      <c r="AL31" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN31" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO31" s="3" t="inlineStr">
+        <is>
+          <t>CDB497</t>
+        </is>
+      </c>
+      <c r="AP31" s="3" t="inlineStr"/>
+      <c r="AQ31" s="3" t="inlineStr"/>
+      <c r="AR31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS31" s="3" t="inlineStr">
+        <is>
+          <t>1h 50m</t>
+        </is>
+      </c>
+      <c r="AT31" s="3" t="inlineStr">
+        <is>
+          <t>8d 15h 40m</t>
+        </is>
+      </c>
+      <c r="AU31" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV31" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW31" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX31" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -6645,10 +6645,8 @@
           <t>Sunil Bishwokarma</t>
         </is>
       </c>
-      <c r="O30" s="3" t="inlineStr">
-        <is>
-          <t>9765209837</t>
-        </is>
+      <c r="O30" s="3" t="n">
+        <v>9765209837</v>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
@@ -6738,10 +6736,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN30" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN30" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO30" s="3" t="inlineStr">
         <is>
@@ -6752,7 +6748,7 @@
       <c r="AQ30" s="3" t="inlineStr"/>
       <c r="AR30" s="3" t="inlineStr">
         <is>
-          <t>Case : iptv issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS30" s="3" t="inlineStr">
@@ -6853,10 +6849,8 @@
           <t>Kamala gharti magar</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
-        <is>
-          <t>9860205079</t>
-        </is>
+      <c r="O31" s="3" t="n">
+        <v>9860205079</v>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
@@ -6942,10 +6936,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN31" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN31" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO31" s="3" t="inlineStr">
         <is>
@@ -6956,7 +6948,7 @@
       <c r="AQ31" s="3" t="inlineStr"/>
       <c r="AR31" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS31" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>19.4%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>22.6%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>10</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>38.7%</t>
         </is>
       </c>
     </row>
@@ -853,13 +853,13 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -1077,13 +1077,13 @@
         <v>3</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX31"/>
+  <dimension ref="A1:AX32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1110,10 +1110,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="38" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="26" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -1143,7 +1143,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -6982,6 +6982,226 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 1:11 PM</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350683</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>Tek Bahadur Budha Magar</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>Tek Bahadur Budha Magar</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>9851192186</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr"/>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:11:52 PM</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr"/>
+      <c r="T32" s="3" t="inlineStr"/>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>9851192186</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 08:09:42 PM</t>
+        </is>
+      </c>
+      <c r="W32" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:11:52 PM</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="inlineStr">
+        <is>
+          <t>27.742863</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA32" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB32" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC32" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD32" s="3" t="inlineStr"/>
+      <c r="AE32" s="3" t="inlineStr">
+        <is>
+          <t>????? ???, Kathmandu 44600 Near By Southwestern State College, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF32" s="3" t="inlineStr">
+        <is>
+          <t>motherisgod60@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG32" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH32" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>03:11 hour</t>
+        </is>
+      </c>
+      <c r="AJ32" s="3" t="inlineStr"/>
+      <c r="AK32" s="3" t="inlineStr"/>
+      <c r="AL32" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN32" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO32" s="3" t="inlineStr">
+        <is>
+          <t>L21-5</t>
+        </is>
+      </c>
+      <c r="AP32" s="3" t="inlineStr">
+        <is>
+          <t>85.325422</t>
+        </is>
+      </c>
+      <c r="AQ32" s="3" t="inlineStr"/>
+      <c r="AR32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>17h 2m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW32" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX32" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>65.6%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>21.9%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>11</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>40.6%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
@@ -859,7 +859,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -1065,7 +1065,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>6</v>
@@ -1083,7 +1083,7 @@
         <v>3</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX32"/>
+  <dimension ref="A1:AX33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7049,10 +7049,8 @@
           <t>Tek Bahadur Budha Magar</t>
         </is>
       </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t>9851192186</t>
-        </is>
+      <c r="O32" s="3" t="n">
+        <v>9851192186</v>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
@@ -7087,10 +7085,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t>27.742863</t>
-        </is>
+      <c r="Y32" s="3" t="n">
+        <v>27.742863</v>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
@@ -7128,10 +7124,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH32" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH32" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI32" s="3" t="inlineStr">
         <is>
@@ -7150,47 +7144,43 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN32" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN32" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO32" s="3" t="inlineStr">
         <is>
           <t>L21-5</t>
         </is>
       </c>
-      <c r="AP32" s="3" t="inlineStr">
-        <is>
-          <t>85.325422</t>
-        </is>
+      <c r="AP32" s="3" t="n">
+        <v>85.325422</v>
       </c>
       <c r="AQ32" s="3" t="inlineStr"/>
       <c r="AR32" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS32" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT32" s="3" t="inlineStr">
+        <is>
+          <t>17h 2m</t>
+        </is>
+      </c>
+      <c r="AU32" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV32" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS32" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT32" s="3" t="inlineStr">
-        <is>
-          <t>17h 2m</t>
-        </is>
-      </c>
-      <c r="AU32" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV32" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="AW32" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -7199,6 +7189,218 @@
       <c r="AX32" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 1:20 PM</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr"/>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348342</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>Niroj Bhakta</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>Niroj Bhakta</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>9841857813</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:59:48 PM</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr"/>
+      <c r="T33" s="3" t="inlineStr"/>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>9841857813</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:59:48 PM</t>
+        </is>
+      </c>
+      <c r="W33" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:20:44 PM</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>27.711324</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA33" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB33" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC33" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD33" s="3" t="inlineStr"/>
+      <c r="AE33" s="3" t="inlineStr">
+        <is>
+          <t>Sitapaila, Nagarjun 44600, Near by Kimdoll and opposite to army camp , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF33" s="3" t="inlineStr"/>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr"/>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>13:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr"/>
+      <c r="AK33" s="3" t="inlineStr"/>
+      <c r="AL33" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN33" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO33" s="3" t="inlineStr">
+        <is>
+          <t>CDB055</t>
+        </is>
+      </c>
+      <c r="AP33" s="3" t="inlineStr">
+        <is>
+          <t>85.286077</t>
+        </is>
+      </c>
+      <c r="AQ33" s="3" t="inlineStr"/>
+      <c r="AR33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>2d 20m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>2d 20m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW33" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX33" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>64.7%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.6%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>13</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>12</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>41.2%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -853,13 +853,13 @@
         <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -949,20 +949,20 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>0</v>
@@ -977,14 +977,14 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -1005,20 +1005,20 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>0</v>
@@ -1033,14 +1033,14 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -1049,7 +1049,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -1059,31 +1059,59 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B11" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="G10" s="4" t="n">
+      <c r="F11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H10" s="4" t="n">
-        <v>24</v>
+      <c r="H11" s="4" t="n">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1097,7 +1125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX33"/>
+  <dimension ref="A1:AX35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7259,10 +7287,8 @@
           <t>Niroj Bhakta</t>
         </is>
       </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>9841857813</t>
-        </is>
+      <c r="O33" s="3" t="n">
+        <v>9841857813</v>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
@@ -7297,10 +7323,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y33" s="3" t="inlineStr">
-        <is>
-          <t>27.711324</t>
-        </is>
+      <c r="Y33" s="3" t="n">
+        <v>27.711324</v>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
@@ -7352,47 +7376,43 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN33" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN33" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO33" s="3" t="inlineStr">
         <is>
           <t>CDB055</t>
         </is>
       </c>
-      <c r="AP33" s="3" t="inlineStr">
-        <is>
-          <t>85.286077</t>
-        </is>
+      <c r="AP33" s="3" t="n">
+        <v>85.28607700000001</v>
       </c>
       <c r="AQ33" s="3" t="inlineStr"/>
       <c r="AR33" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS33" s="3" t="inlineStr">
+        <is>
+          <t>2d 20m</t>
+        </is>
+      </c>
+      <c r="AT33" s="3" t="inlineStr">
+        <is>
+          <t>2d 20m</t>
+        </is>
+      </c>
+      <c r="AU33" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV33" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS33" s="3" t="inlineStr">
-        <is>
-          <t>2d 20m</t>
-        </is>
-      </c>
-      <c r="AT33" s="3" t="inlineStr">
-        <is>
-          <t>2d 20m</t>
-        </is>
-      </c>
-      <c r="AU33" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV33" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW33" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -7401,6 +7421,418 @@
       <c r="AX33" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 1:36 PM</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>WIFI 6</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349975</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Chettri</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>Shanta Chettri</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>9766430374</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr"/>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:36:48 PM</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr"/>
+      <c r="T34" s="3" t="inlineStr"/>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>9866087127</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 01:29:48 PM</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:36:48 PM</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y34" s="3" t="inlineStr"/>
+      <c r="Z34" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA34" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB34" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD34" s="3" t="inlineStr"/>
+      <c r="AE34" s="3" t="inlineStr">
+        <is>
+          <t>Dhapasi - 6, Woda Office Dhapasi - 6, Woda Office, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF34" s="3" t="inlineStr">
+        <is>
+          <t>chettrisudip731@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr"/>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>10:07 hour</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr"/>
+      <c r="AK34" s="3" t="inlineStr"/>
+      <c r="AL34" s="3" t="inlineStr">
+        <is>
+          <t>Bipana Neupane</t>
+        </is>
+      </c>
+      <c r="AM34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN34" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO34" s="3" t="inlineStr">
+        <is>
+          <t>1,14</t>
+        </is>
+      </c>
+      <c r="AP34" s="3" t="inlineStr"/>
+      <c r="AQ34" s="3" t="inlineStr"/>
+      <c r="AR34" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS34" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT34" s="3" t="inlineStr">
+        <is>
+          <t>1d 7m</t>
+        </is>
+      </c>
+      <c r="AU34" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV34" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW34" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX34" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 1:33 PM</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr"/>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>Router faulty</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349776</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t>Yuken Chamling Rai</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>Yuken Chamling Rai</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>9765079317</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr"/>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:33:34 PM</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr"/>
+      <c r="T35" s="3" t="inlineStr"/>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>KLK9765079317</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 11:55:33 AM</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:33:34 PM</t>
+        </is>
+      </c>
+      <c r="X35" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y35" s="3" t="inlineStr"/>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA35" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB35" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC35" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD35" s="3" t="inlineStr"/>
+      <c r="AE35" s="3" t="inlineStr">
+        <is>
+          <t>Khatri Gawn Hatti Gauda - Housing society Q84X+44Q Budhanilkantha 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF35" s="3" t="inlineStr">
+        <is>
+          <t>9765079317@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG35" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH35" s="3" t="inlineStr"/>
+      <c r="AI35" s="3" t="inlineStr"/>
+      <c r="AJ35" s="3" t="inlineStr"/>
+      <c r="AK35" s="3" t="inlineStr"/>
+      <c r="AL35" s="3" t="inlineStr">
+        <is>
+          <t>Bhawana Bista</t>
+        </is>
+      </c>
+      <c r="AM35" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN35" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO35" s="3" t="inlineStr">
+        <is>
+          <t>3,15</t>
+        </is>
+      </c>
+      <c r="AP35" s="3" t="inlineStr"/>
+      <c r="AQ35" s="3" t="inlineStr"/>
+      <c r="AR35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 38m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>22</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>62.9%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>13</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
@@ -859,7 +859,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>6</v>
@@ -1111,7 +1111,7 @@
         <v>3</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1125,7 +1125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX35"/>
+  <dimension ref="A1:AX36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7491,10 +7491,8 @@
           <t>Shanta Chettri</t>
         </is>
       </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t>9766430374</t>
-        </is>
+      <c r="O34" s="3" t="n">
+        <v>9766430374</v>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
@@ -7584,10 +7582,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN34" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN34" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO34" s="3" t="inlineStr">
         <is>
@@ -7598,7 +7594,7 @@
       <c r="AQ34" s="3" t="inlineStr"/>
       <c r="AR34" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI 6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS34" s="3" t="inlineStr">
@@ -7699,10 +7695,8 @@
           <t>Yuken Chamling Rai</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>9765079317</t>
-        </is>
+      <c r="O35" s="3" t="n">
+        <v>9765079317</v>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
@@ -7788,10 +7782,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN35" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN35" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO35" s="3" t="inlineStr">
         <is>
@@ -7802,37 +7794,249 @@
       <c r="AQ35" s="3" t="inlineStr"/>
       <c r="AR35" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS35" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT35" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 38m</t>
+        </is>
+      </c>
+      <c r="AU35" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV35" s="3" t="inlineStr">
+        <is>
           <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS35" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT35" s="3" t="inlineStr">
-        <is>
-          <t>1d 1h 38m</t>
-        </is>
-      </c>
-      <c r="AU35" s="3" t="inlineStr">
+      <c r="AW35" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX35" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 1:41 PM</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349414</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>Ajita Pokhrel</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>Ajita Pokhrel</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>9767478420</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr"/>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 09:01:24 AM</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr"/>
+      <c r="T36" s="3" t="inlineStr"/>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>9851116870</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 09:01:24 AM</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:41:32 PM</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>27.69699</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA36" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB36" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD36" s="3" t="inlineStr"/>
+      <c r="AE36" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki kasthamandap college - -(-)-Lead, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF36" s="3" t="inlineStr">
+        <is>
+          <t>pokhrelajita@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr"/>
+      <c r="AI36" s="3" t="inlineStr"/>
+      <c r="AJ36" s="3" t="inlineStr"/>
+      <c r="AK36" s="3" t="inlineStr"/>
+      <c r="AL36" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN36" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO36" s="3" t="inlineStr">
+        <is>
+          <t>3,8</t>
+        </is>
+      </c>
+      <c r="AP36" s="3" t="inlineStr">
+        <is>
+          <t>85.28057</t>
+        </is>
+      </c>
+      <c r="AQ36" s="3" t="inlineStr"/>
+      <c r="AR36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 40m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 40m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
         <is>
           <t>Other / In Progress (On Hold)</t>
         </is>
       </c>
-      <c r="AV35" s="3" t="inlineStr">
-        <is>
-          <t>Case : Router faulty   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW35" s="3" t="inlineStr">
-        <is>
-          <t>General / Other Issues</t>
-        </is>
-      </c>
-      <c r="AX35" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW36" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX36" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>65.8%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>21.1%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>18.4%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>13</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.7%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -847,10 +847,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="n">
         <v>2</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>4</v>
@@ -859,7 +859,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -977,14 +977,14 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -993,7 +993,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -1005,14 +1005,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1061,7 +1061,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1071,13 +1071,13 @@
         <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -1087,31 +1087,59 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B12" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C12" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D12" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="G12" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>27</v>
+      <c r="H12" s="4" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1125,7 +1153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX36"/>
+  <dimension ref="A1:AX39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -7895,10 +7923,8 @@
           <t>Ajita Pokhrel</t>
         </is>
       </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t>9767478420</t>
-        </is>
+      <c r="O36" s="3" t="n">
+        <v>9767478420</v>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
@@ -7933,10 +7959,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t>27.69699</t>
-        </is>
+      <c r="Y36" s="3" t="n">
+        <v>27.69699</v>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
@@ -7988,47 +8012,43 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN36" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN36" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO36" s="3" t="inlineStr">
         <is>
           <t>3,8</t>
         </is>
       </c>
-      <c r="AP36" s="3" t="inlineStr">
-        <is>
-          <t>85.28057</t>
-        </is>
+      <c r="AP36" s="3" t="n">
+        <v>85.28057</v>
       </c>
       <c r="AQ36" s="3" t="inlineStr"/>
       <c r="AR36" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS36" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 40m</t>
+        </is>
+      </c>
+      <c r="AT36" s="3" t="inlineStr">
+        <is>
+          <t>1d 4h 40m</t>
+        </is>
+      </c>
+      <c r="AU36" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV36" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS36" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 40m</t>
-        </is>
-      </c>
-      <c r="AT36" s="3" t="inlineStr">
-        <is>
-          <t>1d 4h 40m</t>
-        </is>
-      </c>
-      <c r="AU36" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV36" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW36" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -8037,6 +8057,630 @@
       <c r="AX36" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 1:53 PM</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr"/>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348323</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t>KOMA. Digital Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>KOMA. Digital Pvt. Ltd</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>9841504466</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr"/>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:53:23 PM</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr"/>
+      <c r="T37" s="3" t="inlineStr"/>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>9841504466</t>
+        </is>
+      </c>
+      <c r="V37" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 12:47:06 PM</t>
+        </is>
+      </c>
+      <c r="W37" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:53:23 PM</t>
+        </is>
+      </c>
+      <c r="X37" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y37" s="3" t="inlineStr"/>
+      <c r="Z37" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA37" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB37" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC37" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD37" s="3" t="inlineStr"/>
+      <c r="AE37" s="3" t="inlineStr">
+        <is>
+          <t>SubidhaNagar Tinkune - Fast food restaurant M8MW+5MX Pushpa Marg Kathmandu 44600, Kathmandu, Nepal,</t>
+        </is>
+      </c>
+      <c r="AF37" s="3" t="inlineStr">
+        <is>
+          <t>shrestha.nirjal@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG37" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH37" s="3" t="inlineStr"/>
+      <c r="AI37" s="3" t="inlineStr">
+        <is>
+          <t>13:53 hour</t>
+        </is>
+      </c>
+      <c r="AJ37" s="3" t="inlineStr"/>
+      <c r="AK37" s="3" t="inlineStr"/>
+      <c r="AL37" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN37" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO37" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP37" s="3" t="inlineStr"/>
+      <c r="AQ37" s="3" t="inlineStr"/>
+      <c r="AR37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS37" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT37" s="3" t="inlineStr">
+        <is>
+          <t>2d 1h 6m</t>
+        </is>
+      </c>
+      <c r="AU37" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV37" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW37" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX37" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 1:50 PM</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONU Replacement  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>ONU Replacement</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348443</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>Ajay Pandit</t>
+        </is>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>Ajay Pandit</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>9805193735</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:50:41 PM</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr"/>
+      <c r="T38" s="3" t="inlineStr"/>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>CHB9805193736</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:10:40 PM</t>
+        </is>
+      </c>
+      <c r="W38" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:50:41 PM</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y38" s="3" t="inlineStr"/>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA38" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB38" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC38" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD38" s="3" t="inlineStr"/>
+      <c r="AE38" s="3" t="inlineStr">
+        <is>
+          <t>baneshwor, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF38" s="3" t="inlineStr">
+        <is>
+          <t>abcde@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG38" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH38" s="3" t="inlineStr"/>
+      <c r="AI38" s="3" t="inlineStr">
+        <is>
+          <t>13:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ38" s="3" t="inlineStr"/>
+      <c r="AK38" s="3" t="inlineStr"/>
+      <c r="AL38" s="3" t="inlineStr">
+        <is>
+          <t>Hareram Pandit</t>
+        </is>
+      </c>
+      <c r="AM38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN38" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO38" s="3" t="inlineStr">
+        <is>
+          <t>CDB206</t>
+        </is>
+      </c>
+      <c r="AP38" s="3" t="inlineStr"/>
+      <c r="AQ38" s="3" t="inlineStr"/>
+      <c r="AR38" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONU Replacement  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS38" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT38" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 40m</t>
+        </is>
+      </c>
+      <c r="AU38" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV38" s="3" t="inlineStr">
+        <is>
+          <t>Case : ONU Replacement  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW38" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX38" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 1:51 PM</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351041</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>Niraj kami</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>Niraj kami</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>9848502660</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr"/>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:51:30 PM</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr"/>
+      <c r="T39" s="3" t="inlineStr"/>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>9848502660</t>
+        </is>
+      </c>
+      <c r="V39" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 09:49:29 AM</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:51:30 PM</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y39" s="3" t="inlineStr"/>
+      <c r="Z39" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA39" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB39" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC39" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD39" s="3" t="inlineStr"/>
+      <c r="AE39" s="3" t="inlineStr">
+        <is>
+          <t>Twenty Forty - Restaurant P82Q+GXJ Main Road Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF39" s="3" t="inlineStr">
+        <is>
+          <t>nirajankami2300@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr"/>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>03:51 hour</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr"/>
+      <c r="AK39" s="3" t="inlineStr"/>
+      <c r="AL39" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM39" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN39" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO39" s="3" t="inlineStr">
+        <is>
+          <t>L9-6</t>
+        </is>
+      </c>
+      <c r="AP39" s="3" t="inlineStr"/>
+      <c r="AQ39" s="3" t="inlineStr"/>
+      <c r="AR39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS39" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT39" s="3" t="inlineStr">
+        <is>
+          <t>4h 2m</t>
+        </is>
+      </c>
+      <c r="AU39" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV39" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW39" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX39" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -1199,7 +1199,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -8127,10 +8127,8 @@
           <t>KOMA. Digital Pvt. Ltd</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>9841504466</t>
-        </is>
+      <c r="O37" s="3" t="n">
+        <v>9841504466</v>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
@@ -8220,10 +8218,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN37" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN37" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO37" s="3" t="inlineStr">
         <is>
@@ -8234,7 +8230,7 @@
       <c r="AQ37" s="3" t="inlineStr"/>
       <c r="AR37" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS37" s="3" t="inlineStr">
@@ -8335,10 +8331,8 @@
           <t>Ajay Pandit</t>
         </is>
       </c>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>9805193735</t>
-        </is>
+      <c r="O38" s="3" t="n">
+        <v>9805193735</v>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
@@ -8428,10 +8422,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN38" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN38" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO38" s="3" t="inlineStr">
         <is>
@@ -8442,7 +8434,7 @@
       <c r="AQ38" s="3" t="inlineStr"/>
       <c r="AR38" s="3" t="inlineStr">
         <is>
-          <t>Case : ONU Replacement  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS38" s="3" t="inlineStr">
@@ -8543,10 +8535,8 @@
           <t>Niraj kami</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t>9848502660</t>
-        </is>
+      <c r="O39" s="3" t="n">
+        <v>9848502660</v>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
@@ -8636,10 +8626,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN39" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN39" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO39" s="3" t="inlineStr">
         <is>
@@ -8650,7 +8638,7 @@
       <c r="AQ39" s="3" t="inlineStr"/>
       <c r="AR39" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS39" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>67.5%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>17.5%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="C4" s="3" t="n">
-        <v>15</v>
-      </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>47.5%</t>
         </is>
       </c>
     </row>
@@ -847,19 +847,19 @@
         <v>2</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -1127,19 +1127,19 @@
         <v>6</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1153,7 +1153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX39"/>
+  <dimension ref="A1:AX41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1199,7 +1199,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -8672,6 +8672,426 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 2:30 PM</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348509</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>Chiya Mantralaya</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>Chiya Mantralaya</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>9851253424</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr"/>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:30:53 PM</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr"/>
+      <c r="T40" s="3" t="inlineStr"/>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>LTP9851253424</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:49:19 PM</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:30:53 PM</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr"/>
+      <c r="Z40" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA40" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB40" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC40" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD40" s="3" t="inlineStr"/>
+      <c r="AE40" s="3" t="inlineStr">
+        <is>
+          <t>Mahadevstan janta sadak , Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF40" s="3" t="inlineStr">
+        <is>
+          <t>Chiyamatralaya@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG40" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH40" s="3" t="inlineStr"/>
+      <c r="AI40" s="3" t="inlineStr">
+        <is>
+          <t>14:30 hour</t>
+        </is>
+      </c>
+      <c r="AJ40" s="3" t="inlineStr"/>
+      <c r="AK40" s="3" t="inlineStr"/>
+      <c r="AL40" s="3" t="inlineStr">
+        <is>
+          <t>Aashna Pulami</t>
+        </is>
+      </c>
+      <c r="AM40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN40" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO40" s="3" t="inlineStr">
+        <is>
+          <t>CDB603</t>
+        </is>
+      </c>
+      <c r="AP40" s="3" t="inlineStr"/>
+      <c r="AQ40" s="3" t="inlineStr"/>
+      <c r="AR40" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS40" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT40" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 41m</t>
+        </is>
+      </c>
+      <c r="AU40" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV40" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW40" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX40" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 2:27 PM</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341368</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>Ram Bahadur Kuwar</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>Ram Bahadur Kuwar</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>9808622250</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr"/>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:27:50 PM</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr"/>
+      <c r="T41" s="3" t="inlineStr"/>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>DRZ9851241939</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 01:55:53 PM</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:27:50 PM</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y41" s="3" t="inlineStr">
+        <is>
+          <t>27.744472</t>
+        </is>
+      </c>
+      <c r="Z41" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA41" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB41" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC41" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD41" s="3" t="inlineStr"/>
+      <c r="AE41" s="3" t="inlineStr">
+        <is>
+          <t>New Castle Secondary School P8WP+J9H, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF41" s="3" t="inlineStr"/>
+      <c r="AG41" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH41" s="3" t="inlineStr"/>
+      <c r="AI41" s="3" t="inlineStr">
+        <is>
+          <t>22:32 hour</t>
+        </is>
+      </c>
+      <c r="AJ41" s="3" t="inlineStr"/>
+      <c r="AK41" s="3" t="inlineStr"/>
+      <c r="AL41" s="3" t="inlineStr">
+        <is>
+          <t>Aryan Maharjan</t>
+        </is>
+      </c>
+      <c r="AM41" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN41" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO41" s="3" t="inlineStr">
+        <is>
+          <t>L11-5</t>
+        </is>
+      </c>
+      <c r="AP41" s="3" t="inlineStr">
+        <is>
+          <t>85.33042</t>
+        </is>
+      </c>
+      <c r="AQ41" s="3" t="inlineStr"/>
+      <c r="AR41" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>8d 31m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
+          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW41" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX41" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>68.3%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>19.5%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>17.1%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>48.8%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>2</v>
@@ -859,7 +859,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>6</v>
@@ -1139,7 +1139,7 @@
         <v>3</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1153,7 +1153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX41"/>
+  <dimension ref="A1:AX42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -8739,10 +8739,8 @@
           <t>Chiya Mantralaya</t>
         </is>
       </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t>9851253424</t>
-        </is>
+      <c r="O40" s="3" t="n">
+        <v>9851253424</v>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
@@ -8832,10 +8830,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN40" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN40" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO40" s="3" t="inlineStr">
         <is>
@@ -8846,7 +8842,7 @@
       <c r="AQ40" s="3" t="inlineStr"/>
       <c r="AR40" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS40" s="3" t="inlineStr">
@@ -8947,10 +8943,8 @@
           <t>Ram Bahadur Kuwar</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>9808622250</t>
-        </is>
+      <c r="O41" s="3" t="n">
+        <v>9808622250</v>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
@@ -8985,10 +8979,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y41" s="3" t="inlineStr">
-        <is>
-          <t>27.744472</t>
-        </is>
+      <c r="Y41" s="3" t="n">
+        <v>27.744472</v>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
@@ -9040,47 +9032,43 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN41" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN41" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO41" s="3" t="inlineStr">
         <is>
           <t>L11-5</t>
         </is>
       </c>
-      <c r="AP41" s="3" t="inlineStr">
-        <is>
-          <t>85.33042</t>
-        </is>
+      <c r="AP41" s="3" t="n">
+        <v>85.33042</v>
       </c>
       <c r="AQ41" s="3" t="inlineStr"/>
       <c r="AR41" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS41" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT41" s="3" t="inlineStr">
+        <is>
+          <t>8d 31m</t>
+        </is>
+      </c>
+      <c r="AU41" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV41" s="3" t="inlineStr">
+        <is>
           <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS41" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT41" s="3" t="inlineStr">
-        <is>
-          <t>8d 31m</t>
-        </is>
-      </c>
-      <c r="AU41" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV41" s="3" t="inlineStr">
-        <is>
-          <t>Case : WiFi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
       <c r="AW41" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -9089,6 +9077,222 @@
       <c r="AX41" s="3" t="inlineStr">
         <is>
           <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 2:34 PM</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349332</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr">
+        <is>
+          <t>Bishnu Kumar Khadka</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>Bishnu Kumar Khadka</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>9851074853</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr"/>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 08:09:17 AM</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr"/>
+      <c r="T42" s="3" t="inlineStr"/>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>9851074853</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 08:08:08 AM</t>
+        </is>
+      </c>
+      <c r="W42" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:34:36 PM</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y42" s="3" t="inlineStr">
+        <is>
+          <t>27.69419</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA42" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB42" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC42" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD42" s="3" t="inlineStr"/>
+      <c r="AE42" s="3" t="inlineStr">
+        <is>
+          <t>Kalanki Infront of NMB bank building , the building where  Mega Bank is located, Bagmati, Central, N</t>
+        </is>
+      </c>
+      <c r="AF42" s="3" t="inlineStr">
+        <is>
+          <t>bishnuitis@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG42" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH42" s="3" t="inlineStr"/>
+      <c r="AI42" s="3" t="inlineStr">
+        <is>
+          <t>14:34 hour</t>
+        </is>
+      </c>
+      <c r="AJ42" s="3" t="inlineStr"/>
+      <c r="AK42" s="3" t="inlineStr"/>
+      <c r="AL42" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN42" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO42" s="3" t="inlineStr">
+        <is>
+          <t>CDB026</t>
+        </is>
+      </c>
+      <c r="AP42" s="3" t="inlineStr">
+        <is>
+          <t>85.2845</t>
+        </is>
+      </c>
+      <c r="AQ42" s="3" t="inlineStr"/>
+      <c r="AR42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 25m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 26m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW42" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>17.4%</t>
         </is>
       </c>
     </row>
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>6</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>17.1%</t>
+          <t>17.4%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>47.8%</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>4</v>
@@ -853,13 +853,13 @@
         <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -1124,7 +1124,7 @@
         <v>6</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>6</v>
@@ -1133,13 +1133,13 @@
         <v>4</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1153,7 +1153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX42"/>
+  <dimension ref="A1:AX47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -9147,10 +9147,8 @@
           <t>Bishnu Kumar Khadka</t>
         </is>
       </c>
-      <c r="O42" s="3" t="inlineStr">
-        <is>
-          <t>9851074853</t>
-        </is>
+      <c r="O42" s="3" t="n">
+        <v>9851074853</v>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
@@ -9185,10 +9183,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t>27.69419</t>
-        </is>
+      <c r="Y42" s="3" t="n">
+        <v>27.69419</v>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
@@ -9244,53 +9240,893 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN42" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN42" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO42" s="3" t="inlineStr">
         <is>
           <t>CDB026</t>
         </is>
       </c>
-      <c r="AP42" s="3" t="inlineStr">
-        <is>
-          <t>85.2845</t>
-        </is>
+      <c r="AP42" s="3" t="n">
+        <v>85.28449999999999</v>
       </c>
       <c r="AQ42" s="3" t="inlineStr"/>
       <c r="AR42" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS42" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 25m</t>
+        </is>
+      </c>
+      <c r="AT42" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 26m</t>
+        </is>
+      </c>
+      <c r="AU42" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV42" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS42" s="3" t="inlineStr">
-        <is>
-          <t>1d 6h 25m</t>
-        </is>
-      </c>
-      <c r="AT42" s="3" t="inlineStr">
-        <is>
-          <t>1d 6h 26m</t>
-        </is>
-      </c>
-      <c r="AU42" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV42" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW42" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
       <c r="AX42" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 2:49 PM</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347959</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t>Susila Shah</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>Susila Shah</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>9822854396</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr"/>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:49:53 PM</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr"/>
+      <c r="T43" s="3" t="inlineStr"/>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>9822854396</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 09:22:32 AM</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:49:53 PM</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y43" s="3" t="inlineStr">
+        <is>
+          <t>27.75125</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA43" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB43" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC43" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD43" s="3" t="inlineStr"/>
+      <c r="AE43" s="3" t="inlineStr">
+        <is>
+          <t>Nepal Yoga Teacher Training and Retreat Center Goldhunga -5, Kathmandu 44600, Bagmati, Central, Nepa</t>
+        </is>
+      </c>
+      <c r="AF43" s="3" t="inlineStr"/>
+      <c r="AG43" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH43" s="3" t="inlineStr"/>
+      <c r="AI43" s="3" t="inlineStr">
+        <is>
+          <t>14:49 hour</t>
+        </is>
+      </c>
+      <c r="AJ43" s="3" t="inlineStr"/>
+      <c r="AK43" s="3" t="inlineStr"/>
+      <c r="AL43" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN43" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO43" s="3" t="inlineStr">
+        <is>
+          <t>L60-2</t>
+        </is>
+      </c>
+      <c r="AP43" s="3" t="inlineStr">
+        <is>
+          <t>85.286398</t>
+        </is>
+      </c>
+      <c r="AQ43" s="3" t="inlineStr"/>
+      <c r="AR43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS43" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT43" s="3" t="inlineStr">
+        <is>
+          <t>2d 5h 27m</t>
+        </is>
+      </c>
+      <c r="AU43" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV43" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW43" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX43" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 2:51 PM</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>Client is asking for technical team</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349795</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t>Maniraj Singh Maharjan</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>Maniraj Singh Maharjan</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>9823765832</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr"/>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:51:12 PM</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr"/>
+      <c r="T44" s="3" t="inlineStr"/>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>CHB9849220717</t>
+        </is>
+      </c>
+      <c r="V44" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 12:05:36 PM</t>
+        </is>
+      </c>
+      <c r="W44" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:51:12 PM</t>
+        </is>
+      </c>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y44" s="3" t="inlineStr"/>
+      <c r="Z44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA44" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB44" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC44" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD44" s="3" t="inlineStr"/>
+      <c r="AE44" s="3" t="inlineStr">
+        <is>
+          <t>Pako Newroad Tamrakar Complex Near By Tamrakar Complex - Pako Newroad Tamrakar Complex Near By Tamra</t>
+        </is>
+      </c>
+      <c r="AF44" s="3" t="inlineStr">
+        <is>
+          <t>test@test.com</t>
+        </is>
+      </c>
+      <c r="AG44" s="3" t="inlineStr">
+        <is>
+          <t>NETTV-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="AH44" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI44" s="3" t="inlineStr">
+        <is>
+          <t>12:46 hour</t>
+        </is>
+      </c>
+      <c r="AJ44" s="3" t="inlineStr"/>
+      <c r="AK44" s="3" t="inlineStr"/>
+      <c r="AL44" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN44" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO44" s="3" t="inlineStr">
+        <is>
+          <t>CDB161A</t>
+        </is>
+      </c>
+      <c r="AP44" s="3" t="inlineStr"/>
+      <c r="AQ44" s="3" t="inlineStr"/>
+      <c r="AR44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS44" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT44" s="3" t="inlineStr">
+        <is>
+          <t>1d 2h 45m</t>
+        </is>
+      </c>
+      <c r="AU44" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV44" s="3" t="inlineStr">
+        <is>
+          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW44" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX44" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 2:48 PM</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr"/>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341146</t>
+        </is>
+      </c>
+      <c r="K45" s="3" t="inlineStr">
+        <is>
+          <t>Sirjana Gurung</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>Sirjana Gurung</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>9708030031</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q45" s="3" t="inlineStr"/>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:41:13 AM</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr"/>
+      <c r="T45" s="3" t="inlineStr"/>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>CHB9708030031</t>
+        </is>
+      </c>
+      <c r="V45" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:17:20 AM</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:48:50 PM</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y45" s="3" t="inlineStr"/>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA45" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB45" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC45" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD45" s="3" t="inlineStr"/>
+      <c r="AE45" s="3" t="inlineStr">
+        <is>
+          <t>Bhotebahal Futsal - Futsal court M8W6+G76 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF45" s="3" t="inlineStr">
+        <is>
+          <t>9708030031@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG45" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH45" s="3" t="inlineStr"/>
+      <c r="AI45" s="3" t="inlineStr"/>
+      <c r="AJ45" s="3" t="inlineStr"/>
+      <c r="AK45" s="3" t="inlineStr"/>
+      <c r="AL45" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN45" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO45" s="3" t="inlineStr">
+        <is>
+          <t>CDB015</t>
+        </is>
+      </c>
+      <c r="AP45" s="3" t="inlineStr"/>
+      <c r="AQ45" s="3" t="inlineStr"/>
+      <c r="AR45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS45" s="3" t="inlineStr">
+        <is>
+          <t>4h 7m</t>
+        </is>
+      </c>
+      <c r="AT45" s="3" t="inlineStr">
+        <is>
+          <t>8d 3h 31m</t>
+        </is>
+      </c>
+      <c r="AU45" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV45" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW45" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX45" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 2:56 PM</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr"/>
+      <c r="J46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="inlineStr"/>
+      <c r="L46" s="3" t="inlineStr"/>
+      <c r="M46" s="3" t="inlineStr"/>
+      <c r="N46" s="3" t="inlineStr"/>
+      <c r="O46" s="3" t="inlineStr"/>
+      <c r="P46" s="3" t="inlineStr"/>
+      <c r="Q46" s="3" t="inlineStr"/>
+      <c r="R46" s="3" t="inlineStr"/>
+      <c r="S46" s="3" t="inlineStr"/>
+      <c r="T46" s="3" t="inlineStr"/>
+      <c r="U46" s="3" t="inlineStr"/>
+      <c r="V46" s="3" t="inlineStr"/>
+      <c r="W46" s="3" t="inlineStr"/>
+      <c r="X46" s="3" t="inlineStr"/>
+      <c r="Y46" s="3" t="inlineStr"/>
+      <c r="Z46" s="3" t="inlineStr"/>
+      <c r="AA46" s="3" t="inlineStr"/>
+      <c r="AB46" s="3" t="inlineStr"/>
+      <c r="AC46" s="3" t="inlineStr"/>
+      <c r="AD46" s="3" t="inlineStr"/>
+      <c r="AE46" s="3" t="inlineStr"/>
+      <c r="AF46" s="3" t="inlineStr"/>
+      <c r="AG46" s="3" t="inlineStr"/>
+      <c r="AH46" s="3" t="inlineStr"/>
+      <c r="AI46" s="3" t="inlineStr"/>
+      <c r="AJ46" s="3" t="inlineStr"/>
+      <c r="AK46" s="3" t="inlineStr"/>
+      <c r="AL46" s="3" t="inlineStr"/>
+      <c r="AM46" s="3" t="inlineStr"/>
+      <c r="AN46" s="3" t="inlineStr"/>
+      <c r="AO46" s="3" t="inlineStr"/>
+      <c r="AP46" s="3" t="inlineStr"/>
+      <c r="AQ46" s="3" t="inlineStr"/>
+      <c r="AR46" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU46" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV46" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW46" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX46" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 2:55 PM</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr"/>
+      <c r="J47" s="3" t="inlineStr"/>
+      <c r="K47" s="3" t="inlineStr"/>
+      <c r="L47" s="3" t="inlineStr"/>
+      <c r="M47" s="3" t="inlineStr"/>
+      <c r="N47" s="3" t="inlineStr"/>
+      <c r="O47" s="3" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr"/>
+      <c r="Q47" s="3" t="inlineStr"/>
+      <c r="R47" s="3" t="inlineStr"/>
+      <c r="S47" s="3" t="inlineStr"/>
+      <c r="T47" s="3" t="inlineStr"/>
+      <c r="U47" s="3" t="inlineStr"/>
+      <c r="V47" s="3" t="inlineStr"/>
+      <c r="W47" s="3" t="inlineStr"/>
+      <c r="X47" s="3" t="inlineStr"/>
+      <c r="Y47" s="3" t="inlineStr"/>
+      <c r="Z47" s="3" t="inlineStr"/>
+      <c r="AA47" s="3" t="inlineStr"/>
+      <c r="AB47" s="3" t="inlineStr"/>
+      <c r="AC47" s="3" t="inlineStr"/>
+      <c r="AD47" s="3" t="inlineStr"/>
+      <c r="AE47" s="3" t="inlineStr"/>
+      <c r="AF47" s="3" t="inlineStr"/>
+      <c r="AG47" s="3" t="inlineStr"/>
+      <c r="AH47" s="3" t="inlineStr"/>
+      <c r="AI47" s="3" t="inlineStr"/>
+      <c r="AJ47" s="3" t="inlineStr"/>
+      <c r="AK47" s="3" t="inlineStr"/>
+      <c r="AL47" s="3" t="inlineStr"/>
+      <c r="AM47" s="3" t="inlineStr"/>
+      <c r="AN47" s="3" t="inlineStr"/>
+      <c r="AO47" s="3" t="inlineStr"/>
+      <c r="AP47" s="3" t="inlineStr"/>
+      <c r="AQ47" s="3" t="inlineStr"/>
+      <c r="AR47" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU47" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV47" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW47" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX47" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -1199,7 +1199,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -9355,10 +9355,8 @@
           <t>Susila Shah</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t>9822854396</t>
-        </is>
+      <c r="O43" s="3" t="n">
+        <v>9822854396</v>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
@@ -9393,10 +9391,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t>27.75125</t>
-        </is>
+      <c r="Y43" s="3" t="n">
+        <v>27.75125</v>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
@@ -9448,25 +9444,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN43" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN43" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO43" s="3" t="inlineStr">
         <is>
           <t>L60-2</t>
         </is>
       </c>
-      <c r="AP43" s="3" t="inlineStr">
-        <is>
-          <t>85.286398</t>
-        </is>
+      <c r="AP43" s="3" t="n">
+        <v>85.28639800000001</v>
       </c>
       <c r="AQ43" s="3" t="inlineStr"/>
       <c r="AR43" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS43" s="3" t="inlineStr">
@@ -9557,20 +9549,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M44" s="3" t="inlineStr"/>
       <c r="N44" s="3" t="inlineStr">
         <is>
           <t>Maniraj Singh Maharjan</t>
         </is>
       </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t>9823765832</t>
-        </is>
+      <c r="O44" s="3" t="n">
+        <v>9823765832</v>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
@@ -9642,10 +9628,8 @@
           <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
-      <c r="AH44" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH44" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI44" s="3" t="inlineStr">
         <is>
@@ -9664,10 +9648,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN44" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN44" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO44" s="3" t="inlineStr">
         <is>
@@ -9678,7 +9660,7 @@
       <c r="AQ44" s="3" t="inlineStr"/>
       <c r="AR44" s="3" t="inlineStr">
         <is>
-          <t>Case : Client is asking for technical team  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS44" s="3" t="inlineStr">
@@ -9779,10 +9761,8 @@
           <t>Sirjana Gurung</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
-        <is>
-          <t>9708030031</t>
-        </is>
+      <c r="O45" s="3" t="n">
+        <v>9708030031</v>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
@@ -9868,10 +9848,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN45" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN45" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO45" s="3" t="inlineStr">
         <is>
@@ -9882,7 +9860,7 @@
       <c r="AQ45" s="3" t="inlineStr"/>
       <c r="AR45" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS45" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>30</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>61.2%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>16.3%</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>44.9%</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX47"/>
+  <dimension ref="A1:AX50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10110,6 +10110,330 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 3:21 PM</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+      <c r="H48" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr"/>
+      <c r="J48" s="3" t="inlineStr"/>
+      <c r="K48" s="3" t="inlineStr"/>
+      <c r="L48" s="3" t="inlineStr"/>
+      <c r="M48" s="3" t="inlineStr"/>
+      <c r="N48" s="3" t="inlineStr"/>
+      <c r="O48" s="3" t="inlineStr"/>
+      <c r="P48" s="3" t="inlineStr"/>
+      <c r="Q48" s="3" t="inlineStr"/>
+      <c r="R48" s="3" t="inlineStr"/>
+      <c r="S48" s="3" t="inlineStr"/>
+      <c r="T48" s="3" t="inlineStr"/>
+      <c r="U48" s="3" t="inlineStr"/>
+      <c r="V48" s="3" t="inlineStr"/>
+      <c r="W48" s="3" t="inlineStr"/>
+      <c r="X48" s="3" t="inlineStr"/>
+      <c r="Y48" s="3" t="inlineStr"/>
+      <c r="Z48" s="3" t="inlineStr"/>
+      <c r="AA48" s="3" t="inlineStr"/>
+      <c r="AB48" s="3" t="inlineStr"/>
+      <c r="AC48" s="3" t="inlineStr"/>
+      <c r="AD48" s="3" t="inlineStr"/>
+      <c r="AE48" s="3" t="inlineStr"/>
+      <c r="AF48" s="3" t="inlineStr"/>
+      <c r="AG48" s="3" t="inlineStr"/>
+      <c r="AH48" s="3" t="inlineStr"/>
+      <c r="AI48" s="3" t="inlineStr"/>
+      <c r="AJ48" s="3" t="inlineStr"/>
+      <c r="AK48" s="3" t="inlineStr"/>
+      <c r="AL48" s="3" t="inlineStr"/>
+      <c r="AM48" s="3" t="inlineStr"/>
+      <c r="AN48" s="3" t="inlineStr"/>
+      <c r="AO48" s="3" t="inlineStr"/>
+      <c r="AP48" s="3" t="inlineStr"/>
+      <c r="AQ48" s="3" t="inlineStr"/>
+      <c r="AR48" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU48" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV48" s="3" t="inlineStr">
+        <is>
+          <t>Case : For upgradation to wifi6   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW48" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX48" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 3:30 PM</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr"/>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not connecting  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr"/>
+      <c r="J49" s="3" t="inlineStr"/>
+      <c r="K49" s="3" t="inlineStr"/>
+      <c r="L49" s="3" t="inlineStr"/>
+      <c r="M49" s="3" t="inlineStr"/>
+      <c r="N49" s="3" t="inlineStr"/>
+      <c r="O49" s="3" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr"/>
+      <c r="Q49" s="3" t="inlineStr"/>
+      <c r="R49" s="3" t="inlineStr"/>
+      <c r="S49" s="3" t="inlineStr"/>
+      <c r="T49" s="3" t="inlineStr"/>
+      <c r="U49" s="3" t="inlineStr"/>
+      <c r="V49" s="3" t="inlineStr"/>
+      <c r="W49" s="3" t="inlineStr"/>
+      <c r="X49" s="3" t="inlineStr"/>
+      <c r="Y49" s="3" t="inlineStr"/>
+      <c r="Z49" s="3" t="inlineStr"/>
+      <c r="AA49" s="3" t="inlineStr"/>
+      <c r="AB49" s="3" t="inlineStr"/>
+      <c r="AC49" s="3" t="inlineStr"/>
+      <c r="AD49" s="3" t="inlineStr"/>
+      <c r="AE49" s="3" t="inlineStr"/>
+      <c r="AF49" s="3" t="inlineStr"/>
+      <c r="AG49" s="3" t="inlineStr"/>
+      <c r="AH49" s="3" t="inlineStr"/>
+      <c r="AI49" s="3" t="inlineStr"/>
+      <c r="AJ49" s="3" t="inlineStr"/>
+      <c r="AK49" s="3" t="inlineStr"/>
+      <c r="AL49" s="3" t="inlineStr"/>
+      <c r="AM49" s="3" t="inlineStr"/>
+      <c r="AN49" s="3" t="inlineStr"/>
+      <c r="AO49" s="3" t="inlineStr"/>
+      <c r="AP49" s="3" t="inlineStr"/>
+      <c r="AQ49" s="3" t="inlineStr"/>
+      <c r="AR49" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU49" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV49" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not connecting  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW49" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX49" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 3:02 PM</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+      <c r="H50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr"/>
+      <c r="J50" s="3" t="inlineStr"/>
+      <c r="K50" s="3" t="inlineStr"/>
+      <c r="L50" s="3" t="inlineStr"/>
+      <c r="M50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr"/>
+      <c r="O50" s="3" t="inlineStr"/>
+      <c r="P50" s="3" t="inlineStr"/>
+      <c r="Q50" s="3" t="inlineStr"/>
+      <c r="R50" s="3" t="inlineStr"/>
+      <c r="S50" s="3" t="inlineStr"/>
+      <c r="T50" s="3" t="inlineStr"/>
+      <c r="U50" s="3" t="inlineStr"/>
+      <c r="V50" s="3" t="inlineStr"/>
+      <c r="W50" s="3" t="inlineStr"/>
+      <c r="X50" s="3" t="inlineStr"/>
+      <c r="Y50" s="3" t="inlineStr"/>
+      <c r="Z50" s="3" t="inlineStr"/>
+      <c r="AA50" s="3" t="inlineStr"/>
+      <c r="AB50" s="3" t="inlineStr"/>
+      <c r="AC50" s="3" t="inlineStr"/>
+      <c r="AD50" s="3" t="inlineStr"/>
+      <c r="AE50" s="3" t="inlineStr"/>
+      <c r="AF50" s="3" t="inlineStr"/>
+      <c r="AG50" s="3" t="inlineStr"/>
+      <c r="AH50" s="3" t="inlineStr"/>
+      <c r="AI50" s="3" t="inlineStr"/>
+      <c r="AJ50" s="3" t="inlineStr"/>
+      <c r="AK50" s="3" t="inlineStr"/>
+      <c r="AL50" s="3" t="inlineStr"/>
+      <c r="AM50" s="3" t="inlineStr"/>
+      <c r="AN50" s="3" t="inlineStr"/>
+      <c r="AO50" s="3" t="inlineStr"/>
+      <c r="AP50" s="3" t="inlineStr"/>
+      <c r="AQ50" s="3" t="inlineStr"/>
+      <c r="AR50" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS50" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT50" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU50" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV50" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wi-Fi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW50" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX50" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>5</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>60.8%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.7%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>15.7%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>47.1%</t>
         </is>
       </c>
     </row>
@@ -847,19 +847,19 @@
         <v>3</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -1127,19 +1127,19 @@
         <v>7</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" s="4" t="n">
         <v>4</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12" s="4" t="n">
         <v>3</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1153,7 +1153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX50"/>
+  <dimension ref="A1:AX52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1199,7 +1199,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -10434,6 +10434,422 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 3:38 PM</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr"/>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350680</t>
+        </is>
+      </c>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>Nikesh tamang</t>
+        </is>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>Nikesh tamang</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>9808993896</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q51" s="3" t="inlineStr"/>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 03:38:55 PM</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="inlineStr"/>
+      <c r="T51" s="3" t="inlineStr"/>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>9818747627</t>
+        </is>
+      </c>
+      <c r="V51" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 08:06:51 PM</t>
+        </is>
+      </c>
+      <c r="W51" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 03:38:55 PM</t>
+        </is>
+      </c>
+      <c r="X51" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y51" s="3" t="inlineStr"/>
+      <c r="Z51" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA51" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB51" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC51" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD51" s="3" t="inlineStr"/>
+      <c r="AE51" s="3" t="inlineStr">
+        <is>
+          <t>North valley school, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF51" s="3" t="inlineStr"/>
+      <c r="AG51" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH51" s="3" t="inlineStr"/>
+      <c r="AI51" s="3" t="inlineStr">
+        <is>
+          <t>05:38 hour</t>
+        </is>
+      </c>
+      <c r="AJ51" s="3" t="inlineStr"/>
+      <c r="AK51" s="3" t="inlineStr"/>
+      <c r="AL51" s="3" t="inlineStr">
+        <is>
+          <t>Ishlok Shahi</t>
+        </is>
+      </c>
+      <c r="AM51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN51" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO51" s="3" t="inlineStr">
+        <is>
+          <t>L1-6</t>
+        </is>
+      </c>
+      <c r="AP51" s="3" t="inlineStr"/>
+      <c r="AQ51" s="3" t="inlineStr"/>
+      <c r="AR51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS51" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT51" s="3" t="inlineStr">
+        <is>
+          <t>19h 32m</t>
+        </is>
+      </c>
+      <c r="AU51" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV51" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW51" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX51" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 3:35 PM</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+      <c r="H52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341380</t>
+        </is>
+      </c>
+      <c r="K52" s="3" t="inlineStr">
+        <is>
+          <t>Aama Milan Kendra</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Aama Milan Kendra</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>9851220331</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr"/>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 03:35:03 PM</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="inlineStr"/>
+      <c r="T52" s="3" t="inlineStr"/>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>9841863259</t>
+        </is>
+      </c>
+      <c r="V52" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 02:06:54 PM</t>
+        </is>
+      </c>
+      <c r="W52" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 03:35:03 PM</t>
+        </is>
+      </c>
+      <c r="X52" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y52" s="3" t="inlineStr">
+        <is>
+          <t>27.6907</t>
+        </is>
+      </c>
+      <c r="Z52" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA52" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB52" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC52" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD52" s="3" t="inlineStr"/>
+      <c r="AE52" s="3" t="inlineStr">
+        <is>
+          <t>Chakrabarti Habi Education Academy College of Law,Bijulibazar, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF52" s="3" t="inlineStr">
+        <is>
+          <t>workcgnet@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG52" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH52" s="3" t="inlineStr"/>
+      <c r="AI52" s="3" t="inlineStr"/>
+      <c r="AJ52" s="3" t="inlineStr"/>
+      <c r="AK52" s="3" t="inlineStr"/>
+      <c r="AL52" s="3" t="inlineStr">
+        <is>
+          <t>Sabina K.C</t>
+        </is>
+      </c>
+      <c r="AM52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN52" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO52" s="3" t="inlineStr">
+        <is>
+          <t>L48-6</t>
+        </is>
+      </c>
+      <c r="AP52" s="3" t="inlineStr">
+        <is>
+          <t>85.32893</t>
+        </is>
+      </c>
+      <c r="AQ52" s="3" t="inlineStr"/>
+      <c r="AR52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>8d 1h 28m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW52" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX52" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.4%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.4%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>48.1%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>3</v>
@@ -859,7 +859,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3">
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>7</v>
@@ -1139,7 +1139,7 @@
         <v>3</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1153,7 +1153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX52"/>
+  <dimension ref="A1:AX53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -10501,10 +10501,8 @@
           <t>Nikesh tamang</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
-        <is>
-          <t>9808993896</t>
-        </is>
+      <c r="O51" s="3" t="n">
+        <v>9808993896</v>
       </c>
       <c r="P51" s="3" t="inlineStr">
         <is>
@@ -10590,10 +10588,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN51" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN51" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO51" s="3" t="inlineStr">
         <is>
@@ -10604,7 +10600,7 @@
       <c r="AQ51" s="3" t="inlineStr"/>
       <c r="AR51" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS51" s="3" t="inlineStr">
@@ -10705,10 +10701,8 @@
           <t>Aama Milan Kendra</t>
         </is>
       </c>
-      <c r="O52" s="3" t="inlineStr">
-        <is>
-          <t>9851220331</t>
-        </is>
+      <c r="O52" s="3" t="n">
+        <v>9851220331</v>
       </c>
       <c r="P52" s="3" t="inlineStr">
         <is>
@@ -10743,10 +10737,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y52" s="3" t="inlineStr">
-        <is>
-          <t>27.6907</t>
-        </is>
+      <c r="Y52" s="3" t="n">
+        <v>27.6907</v>
       </c>
       <c r="Z52" s="3" t="inlineStr">
         <is>
@@ -10798,47 +10790,43 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN52" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN52" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO52" s="3" t="inlineStr">
         <is>
           <t>L48-6</t>
         </is>
       </c>
-      <c r="AP52" s="3" t="inlineStr">
-        <is>
-          <t>85.32893</t>
-        </is>
+      <c r="AP52" s="3" t="n">
+        <v>85.32893</v>
       </c>
       <c r="AQ52" s="3" t="inlineStr"/>
       <c r="AR52" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS52" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT52" s="3" t="inlineStr">
+        <is>
+          <t>8d 1h 28m</t>
+        </is>
+      </c>
+      <c r="AU52" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV52" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AS52" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT52" s="3" t="inlineStr">
-        <is>
-          <t>8d 1h 28m</t>
-        </is>
-      </c>
-      <c r="AU52" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV52" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgrade  has been updated by Rajesh Maharjan</t>
-        </is>
-      </c>
       <c r="AW52" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -10847,6 +10835,222 @@
       <c r="AX52" s="3" t="inlineStr">
         <is>
           <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 3:51 PM</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351404</t>
+        </is>
+      </c>
+      <c r="K53" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>Cyrus Shrestha</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>9861926855</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr"/>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:18:14 PM</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="inlineStr"/>
+      <c r="T53" s="3" t="inlineStr"/>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>DRZ9861926855</t>
+        </is>
+      </c>
+      <c r="V53" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:18:14 PM</t>
+        </is>
+      </c>
+      <c r="W53" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 03:51:52 PM</t>
+        </is>
+      </c>
+      <c r="X53" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y53" s="3" t="inlineStr">
+        <is>
+          <t>27.70284</t>
+        </is>
+      </c>
+      <c r="Z53" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA53" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB53" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC53" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD53" s="3" t="inlineStr"/>
+      <c r="AE53" s="3" t="inlineStr">
+        <is>
+          <t>Kalimati 27.7027679, 85.2861990 - Near Jehovah's Witnesses Society,Kalimati,Kathmandu - Kathmandu Me</t>
+        </is>
+      </c>
+      <c r="AF53" s="3" t="inlineStr">
+        <is>
+          <t>5sos.cyrus@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG53" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH53" s="3" t="inlineStr"/>
+      <c r="AI53" s="3" t="inlineStr">
+        <is>
+          <t>02:33 hour</t>
+        </is>
+      </c>
+      <c r="AJ53" s="3" t="inlineStr"/>
+      <c r="AK53" s="3" t="inlineStr"/>
+      <c r="AL53" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN53" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO53" s="3" t="inlineStr">
+        <is>
+          <t>2,2</t>
+        </is>
+      </c>
+      <c r="AP53" s="3" t="inlineStr">
+        <is>
+          <t>85.2862</t>
+        </is>
+      </c>
+      <c r="AQ53" s="3" t="inlineStr"/>
+      <c r="AR53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>2h 33m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>2h 33m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW53" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX53" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>58.9%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>16.1%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>84.0%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -841,10 +841,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="n">
         <v>5</v>
@@ -859,7 +859,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
@@ -921,7 +921,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -934,10 +934,10 @@
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -962,10 +962,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -977,7 +977,7 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
@@ -1005,14 +1005,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1033,14 +1033,14 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -1049,7 +1049,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -1061,17 +1061,17 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="E10" s="3" t="n">
         <v>0</v>
@@ -1089,7 +1089,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -1099,13 +1099,13 @@
         <v>0</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
@@ -1115,31 +1115,59 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B13" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E12" s="4" t="n">
+      <c r="E13" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G13" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>38</v>
+      <c r="H13" s="4" t="n">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1153,7 +1181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX53"/>
+  <dimension ref="A1:AX57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1166,10 +1194,10 @@
     <col width="45" customWidth="1" min="8" max="8"/>
     <col width="38" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="26" customWidth="1" min="14" max="14"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -10905,10 +10933,8 @@
           <t>Cyrus Shrestha</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
-        <is>
-          <t>9861926855</t>
-        </is>
+      <c r="O53" s="3" t="n">
+        <v>9861926855</v>
       </c>
       <c r="P53" s="3" t="inlineStr">
         <is>
@@ -10943,10 +10969,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y53" s="3" t="inlineStr">
-        <is>
-          <t>27.70284</t>
-        </is>
+      <c r="Y53" s="3" t="n">
+        <v>27.70284</v>
       </c>
       <c r="Z53" s="3" t="inlineStr">
         <is>
@@ -11002,47 +11026,43 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN53" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN53" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO53" s="3" t="inlineStr">
         <is>
           <t>2,2</t>
         </is>
       </c>
-      <c r="AP53" s="3" t="inlineStr">
-        <is>
-          <t>85.2862</t>
-        </is>
+      <c r="AP53" s="3" t="n">
+        <v>85.28619999999999</v>
       </c>
       <c r="AQ53" s="3" t="inlineStr"/>
       <c r="AR53" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS53" s="3" t="inlineStr">
+        <is>
+          <t>2h 33m</t>
+        </is>
+      </c>
+      <c r="AT53" s="3" t="inlineStr">
+        <is>
+          <t>2h 33m</t>
+        </is>
+      </c>
+      <c r="AU53" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV53" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS53" s="3" t="inlineStr">
-        <is>
-          <t>2h 33m</t>
-        </is>
-      </c>
-      <c r="AT53" s="3" t="inlineStr">
-        <is>
-          <t>2h 33m</t>
-        </is>
-      </c>
-      <c r="AU53" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV53" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW53" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -11051,6 +11071,846 @@
       <c r="AX53" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:16 PM</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347144</t>
+        </is>
+      </c>
+      <c r="K54" s="3" t="inlineStr">
+        <is>
+          <t>Anil Pandey</t>
+        </is>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Anil Pandey</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>9867339967</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q54" s="3" t="inlineStr"/>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:16:22 PM</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="inlineStr"/>
+      <c r="T54" s="3" t="inlineStr"/>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>KLK9867339967</t>
+        </is>
+      </c>
+      <c r="V54" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 11:50:56 AM</t>
+        </is>
+      </c>
+      <c r="W54" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:16:22 PM</t>
+        </is>
+      </c>
+      <c r="X54" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y54" s="3" t="inlineStr"/>
+      <c r="Z54" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA54" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB54" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC54" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD54" s="3" t="inlineStr"/>
+      <c r="AE54" s="3" t="inlineStr">
+        <is>
+          <t>Kirtipur Hospital, Kirtipur Ring Rd, Kathmandu 44618, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF54" s="3" t="inlineStr">
+        <is>
+          <t>apyfx.np@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG54" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH54" s="3" t="inlineStr"/>
+      <c r="AI54" s="3" t="inlineStr"/>
+      <c r="AJ54" s="3" t="inlineStr"/>
+      <c r="AK54" s="3" t="inlineStr"/>
+      <c r="AL54" s="3" t="inlineStr">
+        <is>
+          <t>Sunita Yonjan</t>
+        </is>
+      </c>
+      <c r="AM54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN54" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO54" s="3" t="inlineStr">
+        <is>
+          <t>CDB191</t>
+        </is>
+      </c>
+      <c r="AP54" s="3" t="inlineStr"/>
+      <c r="AQ54" s="3" t="inlineStr"/>
+      <c r="AR54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS54" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT54" s="3" t="inlineStr">
+        <is>
+          <t>3d 4h 25m</t>
+        </is>
+      </c>
+      <c r="AU54" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV54" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW54" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX54" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:11 PM</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr"/>
+      <c r="H55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349548</t>
+        </is>
+      </c>
+      <c r="K55" s="3" t="inlineStr">
+        <is>
+          <t>Hari Saran Karki</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>Hari Saran Karki</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>9841720683</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr"/>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:11:14 PM</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="inlineStr"/>
+      <c r="T55" s="3" t="inlineStr"/>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>9841720683</t>
+        </is>
+      </c>
+      <c r="V55" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 10:07:13 AM</t>
+        </is>
+      </c>
+      <c r="W55" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:11:14 PM</t>
+        </is>
+      </c>
+      <c r="X55" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y55" s="3" t="inlineStr">
+        <is>
+          <t>27.70144</t>
+        </is>
+      </c>
+      <c r="Z55" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA55" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB55" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC55" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD55" s="3" t="inlineStr"/>
+      <c r="AE55" s="3" t="inlineStr">
+        <is>
+          <t>Nearby Sankata Mandir, Shree Ganesh Mandir and Close to Niyetar Sahakari, Te Bahal, Kathmandu, Bagma</t>
+        </is>
+      </c>
+      <c r="AF55" s="3" t="inlineStr">
+        <is>
+          <t>bcs2039@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG55" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH55" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI55" s="3" t="inlineStr">
+        <is>
+          <t>16:04 hour</t>
+        </is>
+      </c>
+      <c r="AJ55" s="3" t="inlineStr"/>
+      <c r="AK55" s="3" t="inlineStr"/>
+      <c r="AL55" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM55" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN55" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO55" s="3" t="inlineStr">
+        <is>
+          <t>1,15</t>
+        </is>
+      </c>
+      <c r="AP55" s="3" t="inlineStr">
+        <is>
+          <t>85.31281</t>
+        </is>
+      </c>
+      <c r="AQ55" s="3" t="inlineStr"/>
+      <c r="AR55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS55" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT55" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 4m</t>
+        </is>
+      </c>
+      <c r="AU55" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV55" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW55" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX55" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:09 PM</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow Internet  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>slow Internet</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348195</t>
+        </is>
+      </c>
+      <c r="K56" s="3" t="inlineStr">
+        <is>
+          <t>Anuj  Kuwar</t>
+        </is>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>Anuj  Kuwar</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>9860614634</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr"/>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:09:31 PM</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="inlineStr"/>
+      <c r="T56" s="3" t="inlineStr"/>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>9860614634</t>
+        </is>
+      </c>
+      <c r="V56" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 11:21:12 AM</t>
+        </is>
+      </c>
+      <c r="W56" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:09:31 PM</t>
+        </is>
+      </c>
+      <c r="X56" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y56" s="3" t="inlineStr"/>
+      <c r="Z56" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA56" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB56" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC56" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD56" s="3" t="inlineStr"/>
+      <c r="AE56" s="3" t="inlineStr">
+        <is>
+          <t>Clicked Location 27.70858, 85.33194 Nearest: CDB436 (45m Road) Map: CG Putalisadak, Bagmati, Nepal,</t>
+        </is>
+      </c>
+      <c r="AF56" s="3" t="inlineStr"/>
+      <c r="AG56" s="3" t="inlineStr">
+        <is>
+          <t>Download &amp; Upload Speed Issue</t>
+        </is>
+      </c>
+      <c r="AH56" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI56" s="3" t="inlineStr"/>
+      <c r="AJ56" s="3" t="inlineStr"/>
+      <c r="AK56" s="3" t="inlineStr"/>
+      <c r="AL56" s="3" t="inlineStr">
+        <is>
+          <t>Sudip Khadka</t>
+        </is>
+      </c>
+      <c r="AM56" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN56" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO56" s="3" t="inlineStr">
+        <is>
+          <t>CDB256</t>
+        </is>
+      </c>
+      <c r="AP56" s="3" t="inlineStr"/>
+      <c r="AQ56" s="3" t="inlineStr"/>
+      <c r="AR56" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow Internet  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS56" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT56" s="3" t="inlineStr">
+        <is>
+          <t>2d 4h 48m</t>
+        </is>
+      </c>
+      <c r="AU56" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV56" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow Internet  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW56" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX56" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:07 PM</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr"/>
+      <c r="H57" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6 Router Upgrade</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351280</t>
+        </is>
+      </c>
+      <c r="K57" s="3" t="inlineStr">
+        <is>
+          <t>Ramjanaki Hydropower Pvt.Ltd.</t>
+        </is>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>Ramjanaki Hydropower Pvt.Ltd.</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>9762414088</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q57" s="3" t="inlineStr"/>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:00:28 PM</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="inlineStr"/>
+      <c r="T57" s="3" t="inlineStr"/>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>mizu_fttx</t>
+        </is>
+      </c>
+      <c r="V57" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:00:14 PM</t>
+        </is>
+      </c>
+      <c r="W57" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:07:08 PM</t>
+        </is>
+      </c>
+      <c r="X57" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y57" s="3" t="inlineStr">
+        <is>
+          <t>27.694534</t>
+        </is>
+      </c>
+      <c r="Z57" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA57" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB57" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC57" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD57" s="3" t="inlineStr"/>
+      <c r="AE57" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Complex, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF57" s="3" t="inlineStr">
+        <is>
+          <t>manoj.pradhan@rameshcorp.com</t>
+        </is>
+      </c>
+      <c r="AG57" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH57" s="3" t="inlineStr"/>
+      <c r="AI57" s="3" t="inlineStr"/>
+      <c r="AJ57" s="3" t="inlineStr"/>
+      <c r="AK57" s="3" t="inlineStr"/>
+      <c r="AL57" s="3" t="inlineStr">
+        <is>
+          <t>Binod Dhami</t>
+        </is>
+      </c>
+      <c r="AM57" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN57" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO57" s="3" t="inlineStr">
+        <is>
+          <t>CDB175</t>
+        </is>
+      </c>
+      <c r="AP57" s="3" t="inlineStr">
+        <is>
+          <t>85.311309</t>
+        </is>
+      </c>
+      <c r="AQ57" s="3" t="inlineStr"/>
+      <c r="AR57" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>4h 6m</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>4h 6m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW57" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX57" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>61.7%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>16.1%</t>
+          <t>18.3%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>13.3%</t>
         </is>
       </c>
     </row>
@@ -752,14 +752,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -856,10 +856,10 @@
         <v>7</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3">
@@ -921,20 +921,20 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -962,10 +962,10 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F6" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -977,14 +977,14 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -996,7 +996,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>1</v>
@@ -1005,14 +1005,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1033,14 +1033,14 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -1049,7 +1049,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -1061,14 +1061,14 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -1089,17 +1089,17 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>0</v>
@@ -1117,7 +1117,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
@@ -1127,13 +1127,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1143,31 +1143,59 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B14" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D14" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E14" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="G13" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>42</v>
+      <c r="G14" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1181,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX57"/>
+  <dimension ref="A1:AX61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -11141,10 +11169,8 @@
           <t>Anil Pandey</t>
         </is>
       </c>
-      <c r="O54" s="3" t="inlineStr">
-        <is>
-          <t>9867339967</t>
-        </is>
+      <c r="O54" s="3" t="n">
+        <v>9867339967</v>
       </c>
       <c r="P54" s="3" t="inlineStr">
         <is>
@@ -11230,10 +11256,8 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN54" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN54" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO54" s="3" t="inlineStr">
         <is>
@@ -11244,7 +11268,7 @@
       <c r="AQ54" s="3" t="inlineStr"/>
       <c r="AR54" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6   has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS54" s="3" t="inlineStr">
@@ -11345,10 +11369,8 @@
           <t>Hari Saran Karki</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
-        <is>
-          <t>9841720683</t>
-        </is>
+      <c r="O55" s="3" t="n">
+        <v>9841720683</v>
       </c>
       <c r="P55" s="3" t="inlineStr">
         <is>
@@ -11383,10 +11405,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y55" s="3" t="inlineStr">
-        <is>
-          <t>27.70144</t>
-        </is>
+      <c r="Y55" s="3" t="n">
+        <v>27.70144</v>
       </c>
       <c r="Z55" s="3" t="inlineStr">
         <is>
@@ -11424,10 +11444,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH55" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH55" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI55" s="3" t="inlineStr">
         <is>
@@ -11446,25 +11464,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN55" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN55" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO55" s="3" t="inlineStr">
         <is>
           <t>1,15</t>
         </is>
       </c>
-      <c r="AP55" s="3" t="inlineStr">
-        <is>
-          <t>85.31281</t>
-        </is>
+      <c r="AP55" s="3" t="n">
+        <v>85.31281</v>
       </c>
       <c r="AQ55" s="3" t="inlineStr"/>
       <c r="AR55" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS55" s="3" t="inlineStr">
@@ -11565,10 +11579,8 @@
           <t>Anuj  Kuwar</t>
         </is>
       </c>
-      <c r="O56" s="3" t="inlineStr">
-        <is>
-          <t>9860614634</t>
-        </is>
+      <c r="O56" s="3" t="n">
+        <v>9860614634</v>
       </c>
       <c r="P56" s="3" t="inlineStr">
         <is>
@@ -11636,10 +11648,8 @@
           <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
-      <c r="AH56" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH56" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI56" s="3" t="inlineStr"/>
       <c r="AJ56" s="3" t="inlineStr"/>
@@ -11654,10 +11664,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN56" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN56" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO56" s="3" t="inlineStr">
         <is>
@@ -11668,7 +11676,7 @@
       <c r="AQ56" s="3" t="inlineStr"/>
       <c r="AR56" s="3" t="inlineStr">
         <is>
-          <t>Case : slow Internet  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS56" s="3" t="inlineStr">
@@ -11769,10 +11777,8 @@
           <t>Ramjanaki Hydropower Pvt.Ltd.</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>9762414088</t>
-        </is>
+      <c r="O57" s="3" t="n">
+        <v>9762414088</v>
       </c>
       <c r="P57" s="3" t="inlineStr">
         <is>
@@ -11807,10 +11813,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y57" s="3" t="inlineStr">
-        <is>
-          <t>27.694534</t>
-        </is>
+      <c r="Y57" s="3" t="n">
+        <v>27.694534</v>
       </c>
       <c r="Z57" s="3" t="inlineStr">
         <is>
@@ -11862,47 +11866,43 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN57" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN57" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO57" s="3" t="inlineStr">
         <is>
           <t>CDB175</t>
         </is>
       </c>
-      <c r="AP57" s="3" t="inlineStr">
-        <is>
-          <t>85.311309</t>
-        </is>
+      <c r="AP57" s="3" t="n">
+        <v>85.31130899999999</v>
       </c>
       <c r="AQ57" s="3" t="inlineStr"/>
       <c r="AR57" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS57" s="3" t="inlineStr">
+        <is>
+          <t>4h 6m</t>
+        </is>
+      </c>
+      <c r="AT57" s="3" t="inlineStr">
+        <is>
+          <t>4h 6m</t>
+        </is>
+      </c>
+      <c r="AU57" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV57" s="3" t="inlineStr">
+        <is>
           <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AS57" s="3" t="inlineStr">
-        <is>
-          <t>4h 6m</t>
-        </is>
-      </c>
-      <c r="AT57" s="3" t="inlineStr">
-        <is>
-          <t>4h 6m</t>
-        </is>
-      </c>
-      <c r="AU57" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV57" s="3" t="inlineStr">
-        <is>
-          <t>Case : WIFI6 Router Upgrade  has been updated by Chandramani Tharu</t>
-        </is>
-      </c>
       <c r="AW57" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -11911,6 +11911,866 @@
       <c r="AX57" s="3" t="inlineStr">
         <is>
           <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:17 PM</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+      <c r="H58" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>slow issue</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348787</t>
+        </is>
+      </c>
+      <c r="K58" s="3" t="inlineStr">
+        <is>
+          <t>Hari Budha</t>
+        </is>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>Hari Budha</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>9716119634</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr"/>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:17:54 PM</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="inlineStr"/>
+      <c r="T58" s="3" t="inlineStr"/>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>BKT9716119634</t>
+        </is>
+      </c>
+      <c r="V58" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 05:50:06 PM</t>
+        </is>
+      </c>
+      <c r="W58" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:17:54 PM</t>
+        </is>
+      </c>
+      <c r="X58" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y58" s="3" t="inlineStr"/>
+      <c r="Z58" s="3" t="inlineStr">
+        <is>
+          <t>Slow Internet Connection</t>
+        </is>
+      </c>
+      <c r="AA58" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB58" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC58" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD58" s="3" t="inlineStr"/>
+      <c r="AE58" s="3" t="inlineStr">
+        <is>
+          <t>Radhe Radhe House - Spiritist center M8GR+RQ2 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF58" s="3" t="inlineStr">
+        <is>
+          <t>9716119634@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG58" s="3" t="inlineStr">
+        <is>
+          <t>Video content is Buffering</t>
+        </is>
+      </c>
+      <c r="AH58" s="3" t="inlineStr"/>
+      <c r="AI58" s="3" t="inlineStr">
+        <is>
+          <t>16:17 hour</t>
+        </is>
+      </c>
+      <c r="AJ58" s="3" t="inlineStr"/>
+      <c r="AK58" s="3" t="inlineStr"/>
+      <c r="AL58" s="3" t="inlineStr">
+        <is>
+          <t>Ayush Basnet</t>
+        </is>
+      </c>
+      <c r="AM58" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN58" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO58" s="3" t="inlineStr">
+        <is>
+          <t>CDB277</t>
+        </is>
+      </c>
+      <c r="AP58" s="3" t="inlineStr"/>
+      <c r="AQ58" s="3" t="inlineStr"/>
+      <c r="AR58" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS58" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT58" s="3" t="inlineStr">
+        <is>
+          <t>1d 22h 27m</t>
+        </is>
+      </c>
+      <c r="AU58" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV58" s="3" t="inlineStr">
+        <is>
+          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW58" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX58" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:27 PM</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr"/>
+      <c r="H59" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not working    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>5g not working</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350460</t>
+        </is>
+      </c>
+      <c r="K59" s="3" t="inlineStr">
+        <is>
+          <t>santoshi shakya</t>
+        </is>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>santoshi shakya</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>9825593167</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr"/>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 05:16:24 PM</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="inlineStr"/>
+      <c r="T59" s="3" t="inlineStr"/>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>9825593167</t>
+        </is>
+      </c>
+      <c r="V59" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 04:59:00 PM</t>
+        </is>
+      </c>
+      <c r="W59" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:27:32 PM</t>
+        </is>
+      </c>
+      <c r="X59" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y59" s="3" t="inlineStr">
+        <is>
+          <t>27.676037</t>
+        </is>
+      </c>
+      <c r="Z59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA59" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB59" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC59" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD59" s="3" t="inlineStr"/>
+      <c r="AE59" s="3" t="inlineStr">
+        <is>
+          <t>Basic Learning English Secondary School - School M6GW+HCQ Chandragiri 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF59" s="3" t="inlineStr">
+        <is>
+          <t>sontoshashkya01@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG59" s="3" t="inlineStr">
+        <is>
+          <t>General Query &amp; Feedback</t>
+        </is>
+      </c>
+      <c r="AH59" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI59" s="3" t="inlineStr">
+        <is>
+          <t>09:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ59" s="3" t="inlineStr"/>
+      <c r="AK59" s="3" t="inlineStr"/>
+      <c r="AL59" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM59" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN59" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO59" s="3" t="inlineStr">
+        <is>
+          <t>CDB461</t>
+        </is>
+      </c>
+      <c r="AP59" s="3" t="inlineStr">
+        <is>
+          <t>85.247317</t>
+        </is>
+      </c>
+      <c r="AQ59" s="3" t="inlineStr"/>
+      <c r="AR59" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not working    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS59" s="3" t="inlineStr">
+        <is>
+          <t>23h 11m</t>
+        </is>
+      </c>
+      <c r="AT59" s="3" t="inlineStr">
+        <is>
+          <t>23h 28m</t>
+        </is>
+      </c>
+      <c r="AU59" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV59" s="3" t="inlineStr">
+        <is>
+          <t>Case : 5g not working    has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW59" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX59" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:25 PM</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+      <c r="H60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>5g not working</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350460</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>santoshi shakya</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>santoshi shakya</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>9825593167</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr"/>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 05:16:24 PM</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="inlineStr"/>
+      <c r="T60" s="3" t="inlineStr"/>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>9825593167</t>
+        </is>
+      </c>
+      <c r="V60" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 04:59:00 PM</t>
+        </is>
+      </c>
+      <c r="W60" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:27:32 PM</t>
+        </is>
+      </c>
+      <c r="X60" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y60" s="3" t="inlineStr">
+        <is>
+          <t>27.676037</t>
+        </is>
+      </c>
+      <c r="Z60" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA60" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB60" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC60" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD60" s="3" t="inlineStr"/>
+      <c r="AE60" s="3" t="inlineStr">
+        <is>
+          <t>Basic Learning English Secondary School - School M6GW+HCQ Chandragiri 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF60" s="3" t="inlineStr">
+        <is>
+          <t>sontoshashkya01@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG60" s="3" t="inlineStr">
+        <is>
+          <t>General Query &amp; Feedback</t>
+        </is>
+      </c>
+      <c r="AH60" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI60" s="3" t="inlineStr">
+        <is>
+          <t>09:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ60" s="3" t="inlineStr"/>
+      <c r="AK60" s="3" t="inlineStr"/>
+      <c r="AL60" s="3" t="inlineStr">
+        <is>
+          <t>Dinesh Rawat</t>
+        </is>
+      </c>
+      <c r="AM60" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN60" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO60" s="3" t="inlineStr">
+        <is>
+          <t>CDB461</t>
+        </is>
+      </c>
+      <c r="AP60" s="3" t="inlineStr">
+        <is>
+          <t>85.247317</t>
+        </is>
+      </c>
+      <c r="AQ60" s="3" t="inlineStr"/>
+      <c r="AR60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS60" s="3" t="inlineStr">
+        <is>
+          <t>23h 11m</t>
+        </is>
+      </c>
+      <c r="AT60" s="3" t="inlineStr">
+        <is>
+          <t>23h 28m</t>
+        </is>
+      </c>
+      <c r="AU60" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV60" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW60" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX60" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:24 PM</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr"/>
+      <c r="H61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>TKT1346312</t>
+        </is>
+      </c>
+      <c r="K61" s="3" t="inlineStr">
+        <is>
+          <t>Basanta Kunwar</t>
+        </is>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>Basanta Kunwar</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>9861900763</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr"/>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:11:18 PM</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="inlineStr"/>
+      <c r="T61" s="3" t="inlineStr"/>
+      <c r="U61" s="3" t="inlineStr">
+        <is>
+          <t>9861900763</t>
+        </is>
+      </c>
+      <c r="V61" s="3" t="inlineStr">
+        <is>
+          <t>25 Sep 2026 04:11:18 PM</t>
+        </is>
+      </c>
+      <c r="W61" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:25:31 PM</t>
+        </is>
+      </c>
+      <c r="X61" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y61" s="3" t="inlineStr"/>
+      <c r="Z61" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA61" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB61" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC61" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD61" s="3" t="inlineStr"/>
+      <c r="AE61" s="3" t="inlineStr">
+        <is>
+          <t>27.688232, 85.271605, Sundarban School Of Science - School, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF61" s="3" t="inlineStr">
+        <is>
+          <t>reetukuor22@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG61" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH61" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI61" s="3" t="inlineStr">
+        <is>
+          <t>06:13 hour</t>
+        </is>
+      </c>
+      <c r="AJ61" s="3" t="inlineStr"/>
+      <c r="AK61" s="3" t="inlineStr"/>
+      <c r="AL61" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM61" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN61" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO61" s="3" t="inlineStr">
+        <is>
+          <t>4,7</t>
+        </is>
+      </c>
+      <c r="AP61" s="3" t="inlineStr"/>
+      <c r="AQ61" s="3" t="inlineStr"/>
+      <c r="AR61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS61" s="3" t="inlineStr">
+        <is>
+          <t>4d 14m</t>
+        </is>
+      </c>
+      <c r="AT61" s="3" t="inlineStr">
+        <is>
+          <t>4d 14m</t>
+        </is>
+      </c>
+      <c r="AU61" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV61" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW61" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX61" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -1255,7 +1255,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -11981,10 +11981,8 @@
           <t>Hari Budha</t>
         </is>
       </c>
-      <c r="O58" s="3" t="inlineStr">
-        <is>
-          <t>9716119634</t>
-        </is>
+      <c r="O58" s="3" t="n">
+        <v>9716119634</v>
       </c>
       <c r="P58" s="3" t="inlineStr">
         <is>
@@ -12074,10 +12072,8 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN58" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN58" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO58" s="3" t="inlineStr">
         <is>
@@ -12088,7 +12084,7 @@
       <c r="AQ58" s="3" t="inlineStr"/>
       <c r="AR58" s="3" t="inlineStr">
         <is>
-          <t>Case : slow issue  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS58" s="3" t="inlineStr">
@@ -12189,10 +12185,8 @@
           <t>santoshi shakya</t>
         </is>
       </c>
-      <c r="O59" s="3" t="inlineStr">
-        <is>
-          <t>9825593167</t>
-        </is>
+      <c r="O59" s="3" t="n">
+        <v>9825593167</v>
       </c>
       <c r="P59" s="3" t="inlineStr">
         <is>
@@ -12227,10 +12221,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y59" s="3" t="inlineStr">
-        <is>
-          <t>27.676037</t>
-        </is>
+      <c r="Y59" s="3" t="n">
+        <v>27.676037</v>
       </c>
       <c r="Z59" s="3" t="inlineStr">
         <is>
@@ -12268,10 +12260,8 @@
           <t>General Query &amp; Feedback</t>
         </is>
       </c>
-      <c r="AH59" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH59" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI59" s="3" t="inlineStr">
         <is>
@@ -12290,25 +12280,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN59" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN59" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO59" s="3" t="inlineStr">
         <is>
           <t>CDB461</t>
         </is>
       </c>
-      <c r="AP59" s="3" t="inlineStr">
-        <is>
-          <t>85.247317</t>
-        </is>
+      <c r="AP59" s="3" t="n">
+        <v>85.247317</v>
       </c>
       <c r="AQ59" s="3" t="inlineStr"/>
       <c r="AR59" s="3" t="inlineStr">
         <is>
-          <t>Case : 5g not working    has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS59" s="3" t="inlineStr">
@@ -12409,10 +12395,8 @@
           <t>santoshi shakya</t>
         </is>
       </c>
-      <c r="O60" s="3" t="inlineStr">
-        <is>
-          <t>9825593167</t>
-        </is>
+      <c r="O60" s="3" t="n">
+        <v>9825593167</v>
       </c>
       <c r="P60" s="3" t="inlineStr">
         <is>
@@ -12447,10 +12431,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y60" s="3" t="inlineStr">
-        <is>
-          <t>27.676037</t>
-        </is>
+      <c r="Y60" s="3" t="n">
+        <v>27.676037</v>
       </c>
       <c r="Z60" s="3" t="inlineStr">
         <is>
@@ -12488,10 +12470,8 @@
           <t>General Query &amp; Feedback</t>
         </is>
       </c>
-      <c r="AH60" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH60" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI60" s="3" t="inlineStr">
         <is>
@@ -12510,25 +12490,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN60" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN60" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO60" s="3" t="inlineStr">
         <is>
           <t>CDB461</t>
         </is>
       </c>
-      <c r="AP60" s="3" t="inlineStr">
-        <is>
-          <t>85.247317</t>
-        </is>
+      <c r="AP60" s="3" t="n">
+        <v>85.247317</v>
       </c>
       <c r="AQ60" s="3" t="inlineStr"/>
       <c r="AR60" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS60" s="3" t="inlineStr">
@@ -12629,10 +12605,8 @@
           <t>Basanta Kunwar</t>
         </is>
       </c>
-      <c r="O61" s="3" t="inlineStr">
-        <is>
-          <t>9861900763</t>
-        </is>
+      <c r="O61" s="3" t="n">
+        <v>9861900763</v>
       </c>
       <c r="P61" s="3" t="inlineStr">
         <is>
@@ -12704,10 +12678,8 @@
           <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
-      <c r="AH61" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH61" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI61" s="3" t="inlineStr">
         <is>
@@ -12726,10 +12698,8 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN61" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN61" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO61" s="3" t="inlineStr">
         <is>
@@ -12740,7 +12710,7 @@
       <c r="AQ61" s="3" t="inlineStr"/>
       <c r="AR61" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS61" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>85.7%</t>
         </is>
       </c>
     </row>
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -622,14 +622,14 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>20.9%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>11.9%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>82.4%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.7%</t>
         </is>
       </c>
     </row>
@@ -844,47 +844,47 @@
         <v>8</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Video content is Buffering</t>
+          <t>Router Damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="6" t="n">
         <v>3</v>
@@ -893,7 +893,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>Video content is Buffering</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -903,25 +903,25 @@
         <v>1</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
       <c r="B5" s="3" t="n">
@@ -940,16 +940,16 @@
         <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -962,16 +962,16 @@
         <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1033,7 +1033,7 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1061,7 +1061,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Router Damage Issue</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1074,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -1117,17 +1117,17 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1145,7 +1145,7 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Welcome Screen Issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
@@ -1155,13 +1155,13 @@
         <v>0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>0</v>
@@ -1180,22 +1180,22 @@
         <v>8</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1209,7 +1209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX61"/>
+  <dimension ref="A1:AX68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1239,7 +1239,7 @@
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
-    <col width="17" customWidth="1" min="28" max="28"/>
+    <col width="21" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
@@ -1254,8 +1254,8 @@
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
-    <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="43" max="43"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="36" customWidth="1" min="47" max="47"/>
@@ -12744,6 +12744,1526 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:52 PM</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>Zg1bIUI+iSmQ1fi360NaxA==</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Adapter damage  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>Router Adapter damage</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>TKT1349489</t>
+        </is>
+      </c>
+      <c r="K62" s="3" t="inlineStr">
+        <is>
+          <t>Mithilesh Thakur</t>
+        </is>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>Mithilesh Thakur</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>9807679964</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q62" s="3" t="inlineStr"/>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 10:01:37 AM</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="inlineStr"/>
+      <c r="T62" s="3" t="inlineStr"/>
+      <c r="U62" s="3" t="inlineStr">
+        <is>
+          <t>9807679964</t>
+        </is>
+      </c>
+      <c r="V62" s="3" t="inlineStr">
+        <is>
+          <t>28 Sep 2026 09:40:11 AM</t>
+        </is>
+      </c>
+      <c r="W62" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:52:31 PM</t>
+        </is>
+      </c>
+      <c r="X62" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y62" s="3" t="inlineStr">
+        <is>
+          <t>27.684118</t>
+        </is>
+      </c>
+      <c r="Z62" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA62" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB62" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC62" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD62" s="3" t="inlineStr"/>
+      <c r="AE62" s="3" t="inlineStr">
+        <is>
+          <t>Armed Police Force Hospital Chandragiri 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF62" s="3" t="inlineStr">
+        <is>
+          <t>mithileshthakur21@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG62" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH62" s="3" t="inlineStr"/>
+      <c r="AI62" s="3" t="inlineStr">
+        <is>
+          <t>16:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ62" s="3" t="inlineStr"/>
+      <c r="AK62" s="3" t="inlineStr"/>
+      <c r="AL62" s="3" t="inlineStr">
+        <is>
+          <t>Sachit Ghimire</t>
+        </is>
+      </c>
+      <c r="AM62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN62" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO62" s="3" t="inlineStr">
+        <is>
+          <t>CDB422</t>
+        </is>
+      </c>
+      <c r="AP62" s="3" t="inlineStr">
+        <is>
+          <t>85.249251</t>
+        </is>
+      </c>
+      <c r="AQ62" s="3" t="inlineStr"/>
+      <c r="AR62" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Adapter damage  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS62" s="3" t="inlineStr">
+        <is>
+          <t>1d 6h 50m</t>
+        </is>
+      </c>
+      <c r="AT62" s="3" t="inlineStr">
+        <is>
+          <t>1d 7h 12m</t>
+        </is>
+      </c>
+      <c r="AU62" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV62" s="3" t="inlineStr">
+        <is>
+          <t>Case : Router Adapter damage  has been updated by Sunil Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW62" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX62" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:50 PM</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G63" s="3" t="inlineStr"/>
+      <c r="H63" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I63" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J63" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350899</t>
+        </is>
+      </c>
+      <c r="K63" s="3" t="inlineStr">
+        <is>
+          <t>Sulaina Shahi</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
+          <t>Sulaina Shahi</t>
+        </is>
+      </c>
+      <c r="O63" s="3" t="inlineStr">
+        <is>
+          <t>9840745095</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q63" s="3" t="inlineStr"/>
+      <c r="R63" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:50:53 PM</t>
+        </is>
+      </c>
+      <c r="S63" s="3" t="inlineStr"/>
+      <c r="T63" s="3" t="inlineStr"/>
+      <c r="U63" s="3" t="inlineStr">
+        <is>
+          <t>9843218118</t>
+        </is>
+      </c>
+      <c r="V63" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 07:40:54 AM</t>
+        </is>
+      </c>
+      <c r="W63" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:50:53 PM</t>
+        </is>
+      </c>
+      <c r="X63" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y63" s="3" t="inlineStr">
+        <is>
+          <t>27.679821</t>
+        </is>
+      </c>
+      <c r="Z63" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA63" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB63" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC63" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD63" s="3" t="inlineStr"/>
+      <c r="AE63" s="3" t="inlineStr">
+        <is>
+          <t>Awareness Int'l Academy,M8JM+625, Bangalamukhi-Sankhamul Rd, Kathmandu ward no 31, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF63" s="3" t="inlineStr">
+        <is>
+          <t>shahisulaina999@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG63" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH63" s="3" t="inlineStr"/>
+      <c r="AI63" s="3" t="inlineStr">
+        <is>
+          <t>06:50 hour</t>
+        </is>
+      </c>
+      <c r="AJ63" s="3" t="inlineStr"/>
+      <c r="AK63" s="3" t="inlineStr"/>
+      <c r="AL63" s="3" t="inlineStr">
+        <is>
+          <t>Nisha Joshi</t>
+        </is>
+      </c>
+      <c r="AM63" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN63" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO63" s="3" t="inlineStr">
+        <is>
+          <t>1,13</t>
+        </is>
+      </c>
+      <c r="AP63" s="3" t="inlineStr">
+        <is>
+          <t>85.332532</t>
+        </is>
+      </c>
+      <c r="AQ63" s="3" t="inlineStr"/>
+      <c r="AR63" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS63" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT63" s="3" t="inlineStr">
+        <is>
+          <t>9h 9m</t>
+        </is>
+      </c>
+      <c r="AU63" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV63" s="3" t="inlineStr">
+        <is>
+          <t>Case :  wifi 6  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW63" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX63" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:01 PM</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+      <c r="H64" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I64" s="3" t="inlineStr">
+        <is>
+          <t>upgrade wifi 6</t>
+        </is>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351481</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>Punam Kumari Shrestha</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
+          <t>Punam Kumari Shrestha</t>
+        </is>
+      </c>
+      <c r="O64" s="3" t="inlineStr">
+        <is>
+          <t>9841879407</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q64" s="3" t="inlineStr"/>
+      <c r="R64" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:01:53 PM</t>
+        </is>
+      </c>
+      <c r="S64" s="3" t="inlineStr"/>
+      <c r="T64" s="3" t="inlineStr"/>
+      <c r="U64" s="3" t="inlineStr">
+        <is>
+          <t>9851167300k</t>
+        </is>
+      </c>
+      <c r="V64" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 02:07:03 PM</t>
+        </is>
+      </c>
+      <c r="W64" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:01:53 PM</t>
+        </is>
+      </c>
+      <c r="X64" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y64" s="3" t="inlineStr">
+        <is>
+          <t>27.69045</t>
+        </is>
+      </c>
+      <c r="Z64" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA64" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB64" s="3" t="inlineStr">
+        <is>
+          <t>MS TICKET  HANDLER</t>
+        </is>
+      </c>
+      <c r="AC64" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD64" s="3" t="inlineStr"/>
+      <c r="AE64" s="3" t="inlineStr">
+        <is>
+          <t>Sanepa ( Inside Ring Road ) Panchakumari Marg, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF64" s="3" t="inlineStr">
+        <is>
+          <t>umeshpunam07@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG64" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH64" s="3" t="inlineStr"/>
+      <c r="AI64" s="3" t="inlineStr">
+        <is>
+          <t>02:54 hour</t>
+        </is>
+      </c>
+      <c r="AJ64" s="3" t="inlineStr"/>
+      <c r="AK64" s="3" t="inlineStr"/>
+      <c r="AL64" s="3" t="inlineStr">
+        <is>
+          <t>Asmita Sunar</t>
+        </is>
+      </c>
+      <c r="AM64" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN64" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO64" s="3" t="inlineStr">
+        <is>
+          <t>CDB682</t>
+        </is>
+      </c>
+      <c r="AP64" s="3" t="inlineStr">
+        <is>
+          <t>85.3063</t>
+        </is>
+      </c>
+      <c r="AQ64" s="3" t="inlineStr"/>
+      <c r="AR64" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS64" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT64" s="3" t="inlineStr">
+        <is>
+          <t>2h 54m</t>
+        </is>
+      </c>
+      <c r="AU64" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV64" s="3" t="inlineStr">
+        <is>
+          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW64" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX64" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:37 PM</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="inlineStr"/>
+      <c r="H65" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I65" s="3" t="inlineStr">
+        <is>
+          <t>no light on the router</t>
+        </is>
+      </c>
+      <c r="J65" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351387</t>
+        </is>
+      </c>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>Ritika Thapa</t>
+        </is>
+      </c>
+      <c r="L65" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
+          <t>Ritika Thapa</t>
+        </is>
+      </c>
+      <c r="O65" s="3" t="inlineStr">
+        <is>
+          <t>9816014031</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q65" s="3" t="inlineStr"/>
+      <c r="R65" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:37:53 PM</t>
+        </is>
+      </c>
+      <c r="S65" s="3" t="inlineStr"/>
+      <c r="T65" s="3" t="inlineStr"/>
+      <c r="U65" s="3" t="inlineStr">
+        <is>
+          <t>CHB9816014031</t>
+        </is>
+      </c>
+      <c r="V65" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 01:09:37 PM</t>
+        </is>
+      </c>
+      <c r="W65" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:37:53 PM</t>
+        </is>
+      </c>
+      <c r="X65" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y65" s="3" t="inlineStr"/>
+      <c r="Z65" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA65" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB65" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC65" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD65" s="3" t="inlineStr"/>
+      <c r="AE65" s="3" t="inlineStr">
+        <is>
+          <t>Mandikatar Heights - Lodge P8PX+J43 Mandikhata Rd Budhanilkantha 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF65" s="3" t="inlineStr">
+        <is>
+          <t>9816014031@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG65" s="3" t="inlineStr">
+        <is>
+          <t>Router Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH65" s="3" t="inlineStr"/>
+      <c r="AI65" s="3" t="inlineStr">
+        <is>
+          <t>03:28 hour</t>
+        </is>
+      </c>
+      <c r="AJ65" s="3" t="inlineStr"/>
+      <c r="AK65" s="3" t="inlineStr"/>
+      <c r="AL65" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM65" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN65" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO65" s="3" t="inlineStr">
+        <is>
+          <t>L55-5A</t>
+        </is>
+      </c>
+      <c r="AP65" s="3" t="inlineStr"/>
+      <c r="AQ65" s="3" t="inlineStr"/>
+      <c r="AR65" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS65" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT65" s="3" t="inlineStr">
+        <is>
+          <t>3h 28m</t>
+        </is>
+      </c>
+      <c r="AU65" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV65" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the router  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW65" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX65" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:25 PM</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+      <c r="H66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wif6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I66" s="3" t="inlineStr">
+        <is>
+          <t>wif6</t>
+        </is>
+      </c>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351319</t>
+        </is>
+      </c>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>Kalyan Adhikari</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
+          <t>Kalyan Adhikari</t>
+        </is>
+      </c>
+      <c r="O66" s="3" t="inlineStr">
+        <is>
+          <t>9841960700</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q66" s="3" t="inlineStr"/>
+      <c r="R66" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="S66" s="3" t="inlineStr"/>
+      <c r="T66" s="3" t="inlineStr"/>
+      <c r="U66" s="3" t="inlineStr">
+        <is>
+          <t>CHB9841960700</t>
+        </is>
+      </c>
+      <c r="V66" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 12:17:31 PM</t>
+        </is>
+      </c>
+      <c r="W66" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:24:59 PM</t>
+        </is>
+      </c>
+      <c r="X66" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y66" s="3" t="inlineStr"/>
+      <c r="Z66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA66" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB66" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC66" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD66" s="3" t="inlineStr"/>
+      <c r="AE66" s="3" t="inlineStr">
+        <is>
+          <t>Saipal Academy Saipal Academy - College Kathmandu 44600, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF66" s="3" t="inlineStr">
+        <is>
+          <t>9841960700@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG66" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH66" s="3" t="inlineStr"/>
+      <c r="AI66" s="3" t="inlineStr">
+        <is>
+          <t>04:08 hour</t>
+        </is>
+      </c>
+      <c r="AJ66" s="3" t="inlineStr"/>
+      <c r="AK66" s="3" t="inlineStr"/>
+      <c r="AL66" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM66" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN66" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO66" s="3" t="inlineStr">
+        <is>
+          <t>L11-5</t>
+        </is>
+      </c>
+      <c r="AP66" s="3" t="inlineStr"/>
+      <c r="AQ66" s="3" t="inlineStr"/>
+      <c r="AR66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wif6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS66" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT66" s="3" t="inlineStr">
+        <is>
+          <t>4h 7m</t>
+        </is>
+      </c>
+      <c r="AU66" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV66" s="3" t="inlineStr">
+        <is>
+          <t>Case : wif6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW66" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX66" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:00 PM</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G67" s="3" t="inlineStr"/>
+      <c r="H67" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I67" s="3" t="inlineStr">
+        <is>
+          <t>iptv issue</t>
+        </is>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>TKT1347646</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Shrestha</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Shrestha</t>
+        </is>
+      </c>
+      <c r="O67" s="3" t="inlineStr">
+        <is>
+          <t>9818815777</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q67" s="3" t="inlineStr"/>
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:00:44 PM</t>
+        </is>
+      </c>
+      <c r="S67" s="3" t="inlineStr"/>
+      <c r="T67" s="3" t="inlineStr"/>
+      <c r="U67" s="3" t="inlineStr">
+        <is>
+          <t>9818815777</t>
+        </is>
+      </c>
+      <c r="V67" s="3" t="inlineStr">
+        <is>
+          <t>26 Sep 2026 07:33:35 PM</t>
+        </is>
+      </c>
+      <c r="W67" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:00:44 PM</t>
+        </is>
+      </c>
+      <c r="X67" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y67" s="3" t="inlineStr">
+        <is>
+          <t>27.72209</t>
+        </is>
+      </c>
+      <c r="Z67" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA67" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB67" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC67" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD67" s="3" t="inlineStr"/>
+      <c r="AE67" s="3" t="inlineStr">
+        <is>
+          <t>Panchdhara Near Kamala beauty parlor , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF67" s="3" t="inlineStr"/>
+      <c r="AG67" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Welcome Screen Issue</t>
+        </is>
+      </c>
+      <c r="AH67" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI67" s="3" t="inlineStr">
+        <is>
+          <t>17:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ67" s="3" t="inlineStr"/>
+      <c r="AK67" s="3" t="inlineStr"/>
+      <c r="AL67" s="3" t="inlineStr">
+        <is>
+          <t>Bashu Bhat</t>
+        </is>
+      </c>
+      <c r="AM67" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN67" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO67" s="3" t="inlineStr">
+        <is>
+          <t>1,4</t>
+        </is>
+      </c>
+      <c r="AP67" s="3" t="inlineStr">
+        <is>
+          <t>85.27905</t>
+        </is>
+      </c>
+      <c r="AQ67" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri
+(29 Sep 2026 05:00:45 PM) :
+TKT1347646
+9818815777
+Sabin Shrestha
+MAC:900EB3C7ED48(new)
+MAC:D0765854CBEB(old)
+Note: user upgrade to WiFi 6 and sky com box doesn'''+'t support ethernet wire.
+Remark  
+Document
+Related Documents</t>
+        </is>
+      </c>
+      <c r="AR67" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri
+(29 Sep 2026 05:00:45 PM) :
+TKT1347646
+9818815777
+Sabin Shrestha
+MAC:900EB3C7ED48(new)
+MAC:D0765854CBEB(old)
+Note: user upgrade to WiFi 6 and sky com box doesn'''+'t support ethernet wire.
+Remark  
+Document
+Related Documents</t>
+        </is>
+      </c>
+      <c r="AS67" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT67" s="3" t="inlineStr">
+        <is>
+          <t>2d 21h 27m</t>
+        </is>
+      </c>
+      <c r="AU67" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV67" s="3" t="inlineStr">
+        <is>
+          <t>Case : iptv issue   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW67" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX67" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 4:31 PM</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+      <c r="H68" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I68" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351071</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>Maya K.C</t>
+        </is>
+      </c>
+      <c r="L68" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
+          <t>Maya K.C</t>
+        </is>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>9841069288</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q68" s="3" t="inlineStr"/>
+      <c r="R68" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:31:53 PM</t>
+        </is>
+      </c>
+      <c r="S68" s="3" t="inlineStr"/>
+      <c r="T68" s="3" t="inlineStr"/>
+      <c r="U68" s="3" t="inlineStr">
+        <is>
+          <t>9841069288</t>
+        </is>
+      </c>
+      <c r="V68" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 10:08:24 AM</t>
+        </is>
+      </c>
+      <c r="W68" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:31:53 PM</t>
+        </is>
+      </c>
+      <c r="X68" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y68" s="3" t="inlineStr">
+        <is>
+          <t>27.73591</t>
+        </is>
+      </c>
+      <c r="Z68" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA68" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB68" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC68" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD68" s="3" t="inlineStr"/>
+      <c r="AE68" s="3" t="inlineStr">
+        <is>
+          <t>Near to NCEB School (???? ???????? ?????? ??????? ?????) ,Kathmandu 44600 , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF68" s="3" t="inlineStr">
+        <is>
+          <t>shishirkc332@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG68" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH68" s="3" t="inlineStr"/>
+      <c r="AI68" s="3" t="inlineStr">
+        <is>
+          <t>06:23 hour</t>
+        </is>
+      </c>
+      <c r="AJ68" s="3" t="inlineStr"/>
+      <c r="AK68" s="3" t="inlineStr"/>
+      <c r="AL68" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM68" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN68" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO68" s="3" t="inlineStr">
+        <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="AP68" s="3" t="inlineStr">
+        <is>
+          <t>85.28792</t>
+        </is>
+      </c>
+      <c r="AQ68" s="3" t="inlineStr"/>
+      <c r="AR68" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS68" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT68" s="3" t="inlineStr">
+        <is>
+          <t>6h 23m</t>
+        </is>
+      </c>
+      <c r="AU68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV68" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW68" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX68" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>61.5%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>7</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>64.8%</t>
         </is>
       </c>
     </row>
@@ -706,19 +706,19 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>9</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>20.9%</t>
+          <t>22.5%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.3%</t>
         </is>
       </c>
     </row>
@@ -752,14 +752,14 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>82.4%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -779,7 +779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
@@ -859,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -977,14 +977,14 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>General Query &amp; Feedback</t>
+          <t>NETTV-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0</v>
@@ -996,7 +996,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="6" t="n">
         <v>1</v>
@@ -1005,7 +1005,7 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Fiber wire breakage suspect</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -1018,10 +1018,10 @@
         <v>0</v>
       </c>
       <c r="E8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="F8" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -1033,14 +1033,14 @@
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Download &amp; Upload Speed Issue</t>
+          <t>General Query &amp; Feedback</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0</v>
@@ -1052,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>1</v>
@@ -1061,7 +1061,7 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB box Damage Issue</t>
+          <t>Fiber wire breakage suspect</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1074,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="E10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -1089,7 +1089,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>Download &amp; Upload Speed Issue</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -1117,17 +1117,17 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>NETTV-Channel buffering,feeze issue</t>
+          <t>Payment Inquiry</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1145,17 +1145,17 @@
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade Dual Band</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>0</v>
@@ -1171,31 +1171,59 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B14" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="C14" s="4" t="n">
+      <c r="B15" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="C15" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="D14" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="E14" s="4" t="n">
+      <c r="D15" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="E15" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F15" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G15" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="H14" s="4" t="n">
-        <v>51</v>
+      <c r="H15" s="4" t="n">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1209,7 +1237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX68"/>
+  <dimension ref="A1:AX72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -12811,10 +12839,8 @@
           <t>Mithilesh Thakur</t>
         </is>
       </c>
-      <c r="O62" s="3" t="inlineStr">
-        <is>
-          <t>9807679964</t>
-        </is>
+      <c r="O62" s="3" t="n">
+        <v>9807679964</v>
       </c>
       <c r="P62" s="3" t="inlineStr">
         <is>
@@ -12849,10 +12875,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y62" s="3" t="inlineStr">
-        <is>
-          <t>27.684118</t>
-        </is>
+      <c r="Y62" s="3" t="n">
+        <v>27.684118</v>
       </c>
       <c r="Z62" s="3" t="inlineStr">
         <is>
@@ -12908,25 +12932,21 @@
           <t>Sunil Chaudhary</t>
         </is>
       </c>
-      <c r="AN62" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN62" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO62" s="3" t="inlineStr">
         <is>
           <t>CDB422</t>
         </is>
       </c>
-      <c r="AP62" s="3" t="inlineStr">
-        <is>
-          <t>85.249251</t>
-        </is>
+      <c r="AP62" s="3" t="n">
+        <v>85.249251</v>
       </c>
       <c r="AQ62" s="3" t="inlineStr"/>
       <c r="AR62" s="3" t="inlineStr">
         <is>
-          <t>Case : Router Adapter damage  has been updated by Sunil Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS62" s="3" t="inlineStr">
@@ -13027,10 +13047,8 @@
           <t>Sulaina Shahi</t>
         </is>
       </c>
-      <c r="O63" s="3" t="inlineStr">
-        <is>
-          <t>9840745095</t>
-        </is>
+      <c r="O63" s="3" t="n">
+        <v>9840745095</v>
       </c>
       <c r="P63" s="3" t="inlineStr">
         <is>
@@ -13065,10 +13083,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y63" s="3" t="inlineStr">
-        <is>
-          <t>27.679821</t>
-        </is>
+      <c r="Y63" s="3" t="n">
+        <v>27.679821</v>
       </c>
       <c r="Z63" s="3" t="inlineStr">
         <is>
@@ -13124,25 +13140,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN63" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN63" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO63" s="3" t="inlineStr">
         <is>
           <t>1,13</t>
         </is>
       </c>
-      <c r="AP63" s="3" t="inlineStr">
-        <is>
-          <t>85.332532</t>
-        </is>
+      <c r="AP63" s="3" t="n">
+        <v>85.332532</v>
       </c>
       <c r="AQ63" s="3" t="inlineStr"/>
       <c r="AR63" s="3" t="inlineStr">
         <is>
-          <t>Case :  wifi 6  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS63" s="3" t="inlineStr">
@@ -13243,10 +13255,8 @@
           <t>Punam Kumari Shrestha</t>
         </is>
       </c>
-      <c r="O64" s="3" t="inlineStr">
-        <is>
-          <t>9841879407</t>
-        </is>
+      <c r="O64" s="3" t="n">
+        <v>9841879407</v>
       </c>
       <c r="P64" s="3" t="inlineStr">
         <is>
@@ -13281,10 +13291,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y64" s="3" t="inlineStr">
-        <is>
-          <t>27.69045</t>
-        </is>
+      <c r="Y64" s="3" t="n">
+        <v>27.69045</v>
       </c>
       <c r="Z64" s="3" t="inlineStr">
         <is>
@@ -13340,25 +13348,21 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN64" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN64" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO64" s="3" t="inlineStr">
         <is>
           <t>CDB682</t>
         </is>
       </c>
-      <c r="AP64" s="3" t="inlineStr">
-        <is>
-          <t>85.3063</t>
-        </is>
+      <c r="AP64" s="3" t="n">
+        <v>85.30629999999999</v>
       </c>
       <c r="AQ64" s="3" t="inlineStr"/>
       <c r="AR64" s="3" t="inlineStr">
         <is>
-          <t>Case : upgrade wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS64" s="3" t="inlineStr">
@@ -13459,10 +13463,8 @@
           <t>Ritika Thapa</t>
         </is>
       </c>
-      <c r="O65" s="3" t="inlineStr">
-        <is>
-          <t>9816014031</t>
-        </is>
+      <c r="O65" s="3" t="n">
+        <v>9816014031</v>
       </c>
       <c r="P65" s="3" t="inlineStr">
         <is>
@@ -13552,10 +13554,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN65" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN65" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO65" s="3" t="inlineStr">
         <is>
@@ -13566,7 +13566,7 @@
       <c r="AQ65" s="3" t="inlineStr"/>
       <c r="AR65" s="3" t="inlineStr">
         <is>
-          <t>Case : no light on the router  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS65" s="3" t="inlineStr">
@@ -13667,10 +13667,8 @@
           <t>Kalyan Adhikari</t>
         </is>
       </c>
-      <c r="O66" s="3" t="inlineStr">
-        <is>
-          <t>9841960700</t>
-        </is>
+      <c r="O66" s="3" t="n">
+        <v>9841960700</v>
       </c>
       <c r="P66" s="3" t="inlineStr">
         <is>
@@ -13760,10 +13758,8 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN66" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN66" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO66" s="3" t="inlineStr">
         <is>
@@ -13774,7 +13770,7 @@
       <c r="AQ66" s="3" t="inlineStr"/>
       <c r="AR66" s="3" t="inlineStr">
         <is>
-          <t>Case : wif6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS66" s="3" t="inlineStr">
@@ -13875,10 +13871,8 @@
           <t>Sabin Shrestha</t>
         </is>
       </c>
-      <c r="O67" s="3" t="inlineStr">
-        <is>
-          <t>9818815777</t>
-        </is>
+      <c r="O67" s="3" t="n">
+        <v>9818815777</v>
       </c>
       <c r="P67" s="3" t="inlineStr">
         <is>
@@ -13913,10 +13907,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y67" s="3" t="inlineStr">
-        <is>
-          <t>27.72209</t>
-        </is>
+      <c r="Y67" s="3" t="n">
+        <v>27.72209</v>
       </c>
       <c r="Z67" s="3" t="inlineStr">
         <is>
@@ -13950,10 +13942,8 @@
           <t>SKYCOM-Welcome Screen Issue</t>
         </is>
       </c>
-      <c r="AH67" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH67" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI67" s="3" t="inlineStr">
         <is>
@@ -13972,20 +13962,16 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN67" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN67" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO67" s="3" t="inlineStr">
         <is>
           <t>1,4</t>
         </is>
       </c>
-      <c r="AP67" s="3" t="inlineStr">
-        <is>
-          <t>85.27905</t>
-        </is>
+      <c r="AP67" s="3" t="n">
+        <v>85.27905</v>
       </c>
       <c r="AQ67" s="3" t="inlineStr">
         <is>
@@ -14115,10 +14101,8 @@
           <t>Maya K.C</t>
         </is>
       </c>
-      <c r="O68" s="3" t="inlineStr">
-        <is>
-          <t>9841069288</t>
-        </is>
+      <c r="O68" s="3" t="n">
+        <v>9841069288</v>
       </c>
       <c r="P68" s="3" t="inlineStr">
         <is>
@@ -14153,10 +14137,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y68" s="3" t="inlineStr">
-        <is>
-          <t>27.73591</t>
-        </is>
+      <c r="Y68" s="3" t="n">
+        <v>27.73591</v>
       </c>
       <c r="Z68" s="3" t="inlineStr">
         <is>
@@ -14212,55 +14194,907 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN68" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN68" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO68" s="3" t="inlineStr">
         <is>
           <t>4,14</t>
         </is>
       </c>
-      <c r="AP68" s="3" t="inlineStr">
-        <is>
-          <t>85.28792</t>
-        </is>
+      <c r="AP68" s="3" t="n">
+        <v>85.28792</v>
       </c>
       <c r="AQ68" s="3" t="inlineStr"/>
       <c r="AR68" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS68" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT68" s="3" t="inlineStr">
+        <is>
+          <t>6h 23m</t>
+        </is>
+      </c>
+      <c r="AU68" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV68" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS68" s="3" t="inlineStr">
+      <c r="AW68" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX68" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:08 PM</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G69" s="3" t="inlineStr"/>
+      <c r="H69" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>interent not working</t>
+        </is>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342441</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>Dex Nine pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="L69" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
+          <t>Dex Nine pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>9865995180</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>Sales / Billing Related Issue</t>
+        </is>
+      </c>
+      <c r="Q69" s="3" t="inlineStr"/>
+      <c r="R69" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:07:40 PM</t>
+        </is>
+      </c>
+      <c r="S69" s="3" t="inlineStr"/>
+      <c r="T69" s="3" t="inlineStr"/>
+      <c r="U69" s="3" t="inlineStr">
+        <is>
+          <t>LTP9700022257</t>
+        </is>
+      </c>
+      <c r="V69" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 01:33:16 PM</t>
+        </is>
+      </c>
+      <c r="W69" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:08:29 PM</t>
+        </is>
+      </c>
+      <c r="X69" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y69" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z69" s="3" t="inlineStr">
+        <is>
+          <t>Sales / Billing Related Issue</t>
+        </is>
+      </c>
+      <c r="AA69" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB69" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC69" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD69" s="3" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="AE69" s="3" t="inlineStr">
+        <is>
+          <t>27.646537000000006, 85.31367780674677, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF69" s="3" t="inlineStr">
+        <is>
+          <t>dexnineco@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG69" s="3" t="inlineStr">
+        <is>
+          <t>Payment Inquiry</t>
+        </is>
+      </c>
+      <c r="AH69" s="3" t="inlineStr"/>
+      <c r="AI69" s="3" t="inlineStr"/>
+      <c r="AJ69" s="3" t="inlineStr"/>
+      <c r="AK69" s="3" t="inlineStr"/>
+      <c r="AL69" s="3" t="inlineStr"/>
+      <c r="AM69" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN69" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO69" s="3" t="inlineStr">
+        <is>
+          <t>CDB517</t>
+        </is>
+      </c>
+      <c r="AP69" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ69" s="3" t="inlineStr"/>
+      <c r="AR69" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS69" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT68" s="3" t="inlineStr">
-        <is>
-          <t>6h 23m</t>
-        </is>
-      </c>
-      <c r="AU68" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV68" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6   has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW68" s="3" t="inlineStr">
+      <c r="AT69" s="3" t="inlineStr">
+        <is>
+          <t>7d 3h 35m</t>
+        </is>
+      </c>
+      <c r="AU69" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV69" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW69" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX69" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:07 PM</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>/Oi+2zlne73U37ZA62PktA==</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>interent not working</t>
+        </is>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>TKT1342441</t>
+        </is>
+      </c>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>Dex Nine pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="L70" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>Self Care</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
+          <t>Dex Nine pvt. Ltd.</t>
+        </is>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>9865995180</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>Sales / Billing Related Issue</t>
+        </is>
+      </c>
+      <c r="Q70" s="3" t="inlineStr"/>
+      <c r="R70" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:07:40 PM</t>
+        </is>
+      </c>
+      <c r="S70" s="3" t="inlineStr"/>
+      <c r="T70" s="3" t="inlineStr"/>
+      <c r="U70" s="3" t="inlineStr">
+        <is>
+          <t>LTP9700022257</t>
+        </is>
+      </c>
+      <c r="V70" s="3" t="inlineStr">
+        <is>
+          <t>22 Sep 2026 01:33:16 PM</t>
+        </is>
+      </c>
+      <c r="W70" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:08:29 PM</t>
+        </is>
+      </c>
+      <c r="X70" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y70" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z70" s="3" t="inlineStr">
+        <is>
+          <t>Sales / Billing Related Issue</t>
+        </is>
+      </c>
+      <c r="AA70" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB70" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC70" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD70" s="3" t="inlineStr">
+        <is>
+          <t>Request</t>
+        </is>
+      </c>
+      <c r="AE70" s="3" t="inlineStr">
+        <is>
+          <t>27.646537000000006, 85.31367780674677, Lalitpur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF70" s="3" t="inlineStr">
+        <is>
+          <t>dexnineco@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG70" s="3" t="inlineStr">
+        <is>
+          <t>Payment Inquiry</t>
+        </is>
+      </c>
+      <c r="AH70" s="3" t="inlineStr"/>
+      <c r="AI70" s="3" t="inlineStr"/>
+      <c r="AJ70" s="3" t="inlineStr"/>
+      <c r="AK70" s="3" t="inlineStr"/>
+      <c r="AL70" s="3" t="inlineStr"/>
+      <c r="AM70" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AN70" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO70" s="3" t="inlineStr">
+        <is>
+          <t>CDB517</t>
+        </is>
+      </c>
+      <c r="AP70" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ70" s="3" t="inlineStr"/>
+      <c r="AR70" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AS70" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT70" s="3" t="inlineStr">
+        <is>
+          <t>7d 3h 35m</t>
+        </is>
+      </c>
+      <c r="AU70" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV70" s="3" t="inlineStr">
+        <is>
+          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+        </is>
+      </c>
+      <c r="AW70" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX70" s="3" t="inlineStr">
+        <is>
+          <t>Rajesh Maharjan</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:17 PM</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G71" s="3" t="inlineStr"/>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348488</t>
+        </is>
+      </c>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>Srijan Dhakal</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
+          <t>Srijan Dhakal</t>
+        </is>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>9818999207</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q71" s="3" t="inlineStr"/>
+      <c r="R71" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:39:24 PM</t>
+        </is>
+      </c>
+      <c r="S71" s="3" t="inlineStr"/>
+      <c r="T71" s="3" t="inlineStr"/>
+      <c r="U71" s="3" t="inlineStr">
+        <is>
+          <t>9818999207</t>
+        </is>
+      </c>
+      <c r="V71" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:39:24 PM</t>
+        </is>
+      </c>
+      <c r="W71" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:17:21 PM</t>
+        </is>
+      </c>
+      <c r="X71" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y71" s="3" t="inlineStr">
+        <is>
+          <t>27.68811</t>
+        </is>
+      </c>
+      <c r="Z71" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA71" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB71" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC71" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD71" s="3" t="inlineStr"/>
+      <c r="AE71" s="3" t="inlineStr">
+        <is>
+          <t>Near to Green Wood Villas,M7PH+QQ4, Kirtipur 44618, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF71" s="3" t="inlineStr">
+        <is>
+          <t>dhakalsrijan59@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG71" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH71" s="3" t="inlineStr"/>
+      <c r="AI71" s="3" t="inlineStr">
+        <is>
+          <t>17:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ71" s="3" t="inlineStr"/>
+      <c r="AK71" s="3" t="inlineStr"/>
+      <c r="AL71" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM71" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN71" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO71" s="3" t="inlineStr">
+        <is>
+          <t>CDB044</t>
+        </is>
+      </c>
+      <c r="AP71" s="3" t="inlineStr">
+        <is>
+          <t>85.280293</t>
+        </is>
+      </c>
+      <c r="AQ71" s="3" t="inlineStr"/>
+      <c r="AR71" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS71" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 37m</t>
+        </is>
+      </c>
+      <c r="AT71" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 37m</t>
+        </is>
+      </c>
+      <c r="AU71" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV71" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW71" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX68" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX71" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:16 PM</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+      <c r="H72" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348488</t>
+        </is>
+      </c>
+      <c r="K72" s="3" t="inlineStr">
+        <is>
+          <t>Srijan Dhakal</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
+          <t>Srijan Dhakal</t>
+        </is>
+      </c>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>9818999207</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q72" s="3" t="inlineStr"/>
+      <c r="R72" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:39:24 PM</t>
+        </is>
+      </c>
+      <c r="S72" s="3" t="inlineStr"/>
+      <c r="T72" s="3" t="inlineStr"/>
+      <c r="U72" s="3" t="inlineStr">
+        <is>
+          <t>9818999207</t>
+        </is>
+      </c>
+      <c r="V72" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:39:24 PM</t>
+        </is>
+      </c>
+      <c r="W72" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:17:21 PM</t>
+        </is>
+      </c>
+      <c r="X72" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y72" s="3" t="inlineStr">
+        <is>
+          <t>27.68811</t>
+        </is>
+      </c>
+      <c r="Z72" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA72" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB72" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC72" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD72" s="3" t="inlineStr"/>
+      <c r="AE72" s="3" t="inlineStr">
+        <is>
+          <t>Near to Green Wood Villas,M7PH+QQ4, Kirtipur 44618, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF72" s="3" t="inlineStr">
+        <is>
+          <t>dhakalsrijan59@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG72" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH72" s="3" t="inlineStr"/>
+      <c r="AI72" s="3" t="inlineStr">
+        <is>
+          <t>17:16 hour</t>
+        </is>
+      </c>
+      <c r="AJ72" s="3" t="inlineStr"/>
+      <c r="AK72" s="3" t="inlineStr"/>
+      <c r="AL72" s="3" t="inlineStr">
+        <is>
+          <t>Joshna Shrestha</t>
+        </is>
+      </c>
+      <c r="AM72" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN72" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO72" s="3" t="inlineStr">
+        <is>
+          <t>CDB044</t>
+        </is>
+      </c>
+      <c r="AP72" s="3" t="inlineStr">
+        <is>
+          <t>85.280293</t>
+        </is>
+      </c>
+      <c r="AQ72" s="3" t="inlineStr"/>
+      <c r="AR72" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS72" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 37m</t>
+        </is>
+      </c>
+      <c r="AT72" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 37m</t>
+        </is>
+      </c>
+      <c r="AU72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV72" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW72" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX72" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>9</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>46</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>63.9%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>22.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>30</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>51.4%</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX72"/>
+  <dimension ref="A1:AX73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -14309,10 +14309,8 @@
           <t>Dex Nine pvt. Ltd.</t>
         </is>
       </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
-          <t>9865995180</t>
-        </is>
+      <c r="O69" s="3" t="n">
+        <v>9865995180</v>
       </c>
       <c r="P69" s="3" t="inlineStr">
         <is>
@@ -14347,10 +14345,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y69" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z69" s="3" t="inlineStr">
         <is>
@@ -14402,25 +14398,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN69" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN69" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO69" s="3" t="inlineStr">
         <is>
           <t>CDB517</t>
         </is>
       </c>
-      <c r="AP69" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP69" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ69" s="3" t="inlineStr"/>
       <c r="AR69" s="3" t="inlineStr">
         <is>
-          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS69" s="3" t="inlineStr">
@@ -14521,10 +14513,8 @@
           <t>Dex Nine pvt. Ltd.</t>
         </is>
       </c>
-      <c r="O70" s="3" t="inlineStr">
-        <is>
-          <t>9865995180</t>
-        </is>
+      <c r="O70" s="3" t="n">
+        <v>9865995180</v>
       </c>
       <c r="P70" s="3" t="inlineStr">
         <is>
@@ -14559,10 +14549,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y70" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="Y70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="Z70" s="3" t="inlineStr">
         <is>
@@ -14614,25 +14602,21 @@
           <t>Rajesh Maharjan</t>
         </is>
       </c>
-      <c r="AN70" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN70" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO70" s="3" t="inlineStr">
         <is>
           <t>CDB517</t>
         </is>
       </c>
-      <c r="AP70" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="AP70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="AQ70" s="3" t="inlineStr"/>
       <c r="AR70" s="3" t="inlineStr">
         <is>
-          <t>Case : interent not working  has been updated by Rajesh Maharjan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS70" s="3" t="inlineStr">
@@ -14733,10 +14717,8 @@
           <t>Srijan Dhakal</t>
         </is>
       </c>
-      <c r="O71" s="3" t="inlineStr">
-        <is>
-          <t>9818999207</t>
-        </is>
+      <c r="O71" s="3" t="n">
+        <v>9818999207</v>
       </c>
       <c r="P71" s="3" t="inlineStr">
         <is>
@@ -14771,10 +14753,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y71" s="3" t="inlineStr">
-        <is>
-          <t>27.68811</t>
-        </is>
+      <c r="Y71" s="3" t="n">
+        <v>27.68811</v>
       </c>
       <c r="Z71" s="3" t="inlineStr">
         <is>
@@ -14830,25 +14810,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN71" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN71" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO71" s="3" t="inlineStr">
         <is>
           <t>CDB044</t>
         </is>
       </c>
-      <c r="AP71" s="3" t="inlineStr">
-        <is>
-          <t>85.280293</t>
-        </is>
+      <c r="AP71" s="3" t="n">
+        <v>85.280293</v>
       </c>
       <c r="AQ71" s="3" t="inlineStr"/>
       <c r="AR71" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS71" s="3" t="inlineStr">
@@ -14949,10 +14925,8 @@
           <t>Srijan Dhakal</t>
         </is>
       </c>
-      <c r="O72" s="3" t="inlineStr">
-        <is>
-          <t>9818999207</t>
-        </is>
+      <c r="O72" s="3" t="n">
+        <v>9818999207</v>
       </c>
       <c r="P72" s="3" t="inlineStr">
         <is>
@@ -14987,10 +14961,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y72" s="3" t="inlineStr">
-        <is>
-          <t>27.68811</t>
-        </is>
+      <c r="Y72" s="3" t="n">
+        <v>27.68811</v>
       </c>
       <c r="Z72" s="3" t="inlineStr">
         <is>
@@ -15046,47 +15018,43 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN72" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN72" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO72" s="3" t="inlineStr">
         <is>
           <t>CDB044</t>
         </is>
       </c>
-      <c r="AP72" s="3" t="inlineStr">
-        <is>
-          <t>85.280293</t>
-        </is>
+      <c r="AP72" s="3" t="n">
+        <v>85.280293</v>
       </c>
       <c r="AQ72" s="3" t="inlineStr"/>
       <c r="AR72" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS72" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 37m</t>
+        </is>
+      </c>
+      <c r="AT72" s="3" t="inlineStr">
+        <is>
+          <t>2d 2h 37m</t>
+        </is>
+      </c>
+      <c r="AU72" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV72" s="3" t="inlineStr">
+        <is>
           <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AS72" s="3" t="inlineStr">
-        <is>
-          <t>2d 2h 37m</t>
-        </is>
-      </c>
-      <c r="AT72" s="3" t="inlineStr">
-        <is>
-          <t>2d 2h 37m</t>
-        </is>
-      </c>
-      <c r="AU72" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Closed)</t>
-        </is>
-      </c>
-      <c r="AV72" s="3" t="inlineStr">
-        <is>
-          <t>Case : Wifi 6  has been updated by Ajit Shrestha</t>
-        </is>
-      </c>
       <c r="AW72" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -15095,6 +15063,210 @@
       <c r="AX72" s="3" t="inlineStr">
         <is>
           <t>Ajit Shrestha</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:19 PM</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G73" s="3" t="inlineStr"/>
+      <c r="H73" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>TKT1348423</t>
+        </is>
+      </c>
+      <c r="K73" s="3" t="inlineStr">
+        <is>
+          <t>Prem Bahadur Kunwar</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
+          <t>Prem Bahadur Kunwar</t>
+        </is>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>9841458042</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q73" s="3" t="inlineStr"/>
+      <c r="R73" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:19:37 PM</t>
+        </is>
+      </c>
+      <c r="S73" s="3" t="inlineStr"/>
+      <c r="T73" s="3" t="inlineStr"/>
+      <c r="U73" s="3" t="inlineStr">
+        <is>
+          <t>9841458042</t>
+        </is>
+      </c>
+      <c r="V73" s="3" t="inlineStr">
+        <is>
+          <t>27 Sep 2026 02:01:08 PM</t>
+        </is>
+      </c>
+      <c r="W73" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:19:37 PM</t>
+        </is>
+      </c>
+      <c r="X73" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y73" s="3" t="inlineStr"/>
+      <c r="Z73" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA73" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB73" s="3" t="inlineStr">
+        <is>
+          <t>Suraj Mainali</t>
+        </is>
+      </c>
+      <c r="AC73" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD73" s="3" t="inlineStr"/>
+      <c r="AE73" s="3" t="inlineStr">
+        <is>
+          <t>Shree Manohar Secondary School - Community school P8P9+XPM Tokha 44600, , ,</t>
+        </is>
+      </c>
+      <c r="AF73" s="3" t="inlineStr">
+        <is>
+          <t>kunwarprem849@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG73" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH73" s="3" t="inlineStr"/>
+      <c r="AI73" s="3" t="inlineStr"/>
+      <c r="AJ73" s="3" t="inlineStr"/>
+      <c r="AK73" s="3" t="inlineStr"/>
+      <c r="AL73" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM73" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN73" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO73" s="3" t="inlineStr">
+        <is>
+          <t>L55-5</t>
+        </is>
+      </c>
+      <c r="AP73" s="3" t="inlineStr"/>
+      <c r="AQ73" s="3" t="inlineStr"/>
+      <c r="AR73" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS73" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT73" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 18m</t>
+        </is>
+      </c>
+      <c r="AU73" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV73" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW73" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX73" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>64.3%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.9%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.6%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.8%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>52.7%</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>6</v>
@@ -859,7 +859,7 @@
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>11</v>
@@ -1223,7 +1223,7 @@
         <v>6</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX73"/>
+  <dimension ref="A1:AX75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15133,10 +15133,8 @@
           <t>Prem Bahadur Kunwar</t>
         </is>
       </c>
-      <c r="O73" s="3" t="inlineStr">
-        <is>
-          <t>9841458042</t>
-        </is>
+      <c r="O73" s="3" t="n">
+        <v>9841458042</v>
       </c>
       <c r="P73" s="3" t="inlineStr">
         <is>
@@ -15222,10 +15220,8 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN73" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN73" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO73" s="3" t="inlineStr">
         <is>
@@ -15236,37 +15232,457 @@
       <c r="AQ73" s="3" t="inlineStr"/>
       <c r="AR73" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS73" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT73" s="3" t="inlineStr">
+        <is>
+          <t>2d 3h 18m</t>
+        </is>
+      </c>
+      <c r="AU73" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV73" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AS73" s="3" t="inlineStr">
+      <c r="AW73" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX73" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:37 PM</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>atwz5SElGeKMz8qxsp3b6c34SBAfIMR+</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr"/>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>TKT1341146</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>Sirjana Gurung</t>
+        </is>
+      </c>
+      <c r="L74" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
+          <t>Sirjana Gurung</t>
+        </is>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>9708030031</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q74" s="3" t="inlineStr"/>
+      <c r="R74" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:37:35 PM</t>
+        </is>
+      </c>
+      <c r="S74" s="3" t="inlineStr"/>
+      <c r="T74" s="3" t="inlineStr"/>
+      <c r="U74" s="3" t="inlineStr">
+        <is>
+          <t>CHB9708030031</t>
+        </is>
+      </c>
+      <c r="V74" s="3" t="inlineStr">
+        <is>
+          <t>21 Sep 2026 11:17:20 AM</t>
+        </is>
+      </c>
+      <c r="W74" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:37:35 PM</t>
+        </is>
+      </c>
+      <c r="X74" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y74" s="3" t="inlineStr"/>
+      <c r="Z74" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA74" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB74" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC74" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD74" s="3" t="inlineStr"/>
+      <c r="AE74" s="3" t="inlineStr">
+        <is>
+          <t>Bhotebahal Futsal - Futsal court M8W6+G76 Kathmandu 44600, Kathmandu, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF74" s="3" t="inlineStr">
+        <is>
+          <t>9708030031@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG74" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH74" s="3" t="inlineStr"/>
+      <c r="AI74" s="3" t="inlineStr">
+        <is>
+          <t>04:20 hour</t>
+        </is>
+      </c>
+      <c r="AJ74" s="3" t="inlineStr"/>
+      <c r="AK74" s="3" t="inlineStr"/>
+      <c r="AL74" s="3" t="inlineStr">
+        <is>
+          <t>Monali Lohani</t>
+        </is>
+      </c>
+      <c r="AM74" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AN74" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO74" s="3" t="inlineStr">
+        <is>
+          <t>CDB015</t>
+        </is>
+      </c>
+      <c r="AP74" s="3" t="inlineStr"/>
+      <c r="AQ74" s="3" t="inlineStr"/>
+      <c r="AR74" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AS74" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT73" s="3" t="inlineStr">
-        <is>
-          <t>2d 3h 18m</t>
-        </is>
-      </c>
-      <c r="AU73" s="3" t="inlineStr">
-        <is>
-          <t>Other / In Progress (On Hold)</t>
-        </is>
-      </c>
-      <c r="AV73" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sanjeev Giri</t>
-        </is>
-      </c>
-      <c r="AW73" s="3" t="inlineStr">
+      <c r="AT74" s="3" t="inlineStr">
+        <is>
+          <t>8d 6h 20m</t>
+        </is>
+      </c>
+      <c r="AU74" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV74" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+        </is>
+      </c>
+      <c r="AW74" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
         </is>
       </c>
-      <c r="AX73" s="3" t="inlineStr">
-        <is>
-          <t>Sanjeev Giri</t>
+      <c r="AX74" s="3" t="inlineStr">
+        <is>
+          <t>Chandramani Tharu</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 5:45 PM</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>KK1e4rFHODw22QGqrKXwiw==</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G75" s="3" t="inlineStr"/>
+      <c r="H75" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>TKT1350858</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="inlineStr">
+        <is>
+          <t>Raj Kumar Bhatta</t>
+        </is>
+      </c>
+      <c r="L75" s="3" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
+          <t>Raj Kumar Bhatta</t>
+        </is>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>9851281562</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q75" s="3" t="inlineStr"/>
+      <c r="R75" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 06:23:39 AM</t>
+        </is>
+      </c>
+      <c r="S75" s="3" t="inlineStr"/>
+      <c r="T75" s="3" t="inlineStr"/>
+      <c r="U75" s="3" t="inlineStr">
+        <is>
+          <t>9851281562</t>
+        </is>
+      </c>
+      <c r="V75" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 06:23:39 AM</t>
+        </is>
+      </c>
+      <c r="W75" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 05:45:52 PM</t>
+        </is>
+      </c>
+      <c r="X75" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y75" s="3" t="inlineStr">
+        <is>
+          <t>27.671466</t>
+        </is>
+      </c>
+      <c r="Z75" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA75" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-</t>
+        </is>
+      </c>
+      <c r="AB75" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC75" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD75" s="3" t="inlineStr"/>
+      <c r="AE75" s="3" t="inlineStr">
+        <is>
+          <t>near Subhakamana Party Palace Kirtipur, M7FJ+QWF, Panga Ma Vi Rd, Kirtipur 44600, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF75" s="3" t="inlineStr"/>
+      <c r="AG75" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH75" s="3" t="inlineStr"/>
+      <c r="AI75" s="3" t="inlineStr">
+        <is>
+          <t>07:45 hour</t>
+        </is>
+      </c>
+      <c r="AJ75" s="3" t="inlineStr"/>
+      <c r="AK75" s="3" t="inlineStr"/>
+      <c r="AL75" s="3" t="inlineStr">
+        <is>
+          <t>Sandesh Ghale</t>
+        </is>
+      </c>
+      <c r="AM75" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AN75" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO75" s="3" t="inlineStr">
+        <is>
+          <t>3,13</t>
+        </is>
+      </c>
+      <c r="AP75" s="3" t="inlineStr">
+        <is>
+          <t>85.282949</t>
+        </is>
+      </c>
+      <c r="AQ75" s="3" t="inlineStr"/>
+      <c r="AR75" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AS75" s="3" t="inlineStr">
+        <is>
+          <t>11h 22m</t>
+        </is>
+      </c>
+      <c r="AT75" s="3" t="inlineStr">
+        <is>
+          <t>11h 22m</t>
+        </is>
+      </c>
+      <c r="AU75" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Closed)</t>
+        </is>
+      </c>
+      <c r="AV75" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+        </is>
+      </c>
+      <c r="AW75" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX75" s="3" t="inlineStr">
+        <is>
+          <t>Ajit Shrestha</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -15333,10 +15333,8 @@
           <t>Sirjana Gurung</t>
         </is>
       </c>
-      <c r="O74" s="3" t="inlineStr">
-        <is>
-          <t>9708030031</t>
-        </is>
+      <c r="O74" s="3" t="n">
+        <v>9708030031</v>
       </c>
       <c r="P74" s="3" t="inlineStr">
         <is>
@@ -15426,10 +15424,8 @@
           <t>Chandramani Tharu</t>
         </is>
       </c>
-      <c r="AN74" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN74" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO74" s="3" t="inlineStr">
         <is>
@@ -15440,7 +15436,7 @@
       <c r="AQ74" s="3" t="inlineStr"/>
       <c r="AR74" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Chandramani Tharu</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS74" s="3" t="inlineStr">
@@ -15541,10 +15537,8 @@
           <t>Raj Kumar Bhatta</t>
         </is>
       </c>
-      <c r="O75" s="3" t="inlineStr">
-        <is>
-          <t>9851281562</t>
-        </is>
+      <c r="O75" s="3" t="n">
+        <v>9851281562</v>
       </c>
       <c r="P75" s="3" t="inlineStr">
         <is>
@@ -15579,10 +15573,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y75" s="3" t="inlineStr">
-        <is>
-          <t>27.671466</t>
-        </is>
+      <c r="Y75" s="3" t="n">
+        <v>27.671466</v>
       </c>
       <c r="Z75" s="3" t="inlineStr">
         <is>
@@ -15634,25 +15626,21 @@
           <t>Ajit Shrestha</t>
         </is>
       </c>
-      <c r="AN75" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN75" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO75" s="3" t="inlineStr">
         <is>
           <t>3,13</t>
         </is>
       </c>
-      <c r="AP75" s="3" t="inlineStr">
-        <is>
-          <t>85.282949</t>
-        </is>
+      <c r="AP75" s="3" t="n">
+        <v>85.282949</v>
       </c>
       <c r="AQ75" s="3" t="inlineStr"/>
       <c r="AR75" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Ajit Shrestha</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS75" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -604,14 +604,14 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.5%</t>
         </is>
       </c>
     </row>
@@ -640,14 +640,14 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.3%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.3%</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
     </row>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
     </row>
@@ -853,13 +853,13 @@
         <v>3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>3</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -1217,13 +1217,13 @@
         <v>6</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15" s="4" t="n">
         <v>6</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX75"/>
+  <dimension ref="A1:AX76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -15674,6 +15674,222 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 7:07 PM</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>e9R6tm2jVXzJtWahLoJ2dw==</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr"/>
+      <c r="H76" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 Router</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>TKT1351709</t>
+        </is>
+      </c>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t>Rakesh shrestha</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
+          <t>Rakesh shrestha</t>
+        </is>
+      </c>
+      <c r="O76" s="3" t="inlineStr">
+        <is>
+          <t>9813632008</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q76" s="3" t="inlineStr"/>
+      <c r="R76" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 07:07:28 PM</t>
+        </is>
+      </c>
+      <c r="S76" s="3" t="inlineStr"/>
+      <c r="T76" s="3" t="inlineStr"/>
+      <c r="U76" s="3" t="inlineStr">
+        <is>
+          <t>9813632008</t>
+        </is>
+      </c>
+      <c r="V76" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 04:53:59 PM</t>
+        </is>
+      </c>
+      <c r="W76" s="3" t="inlineStr">
+        <is>
+          <t>29 Sep 2026 07:07:28 PM</t>
+        </is>
+      </c>
+      <c r="X76" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y76" s="3" t="inlineStr">
+        <is>
+          <t>27.717205</t>
+        </is>
+      </c>
+      <c r="Z76" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA76" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB76" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC76" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD76" s="3" t="inlineStr"/>
+      <c r="AE76" s="3" t="inlineStr">
+        <is>
+          <t>Samata Shiksha Niketan School , P986+R99, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF76" s="3" t="inlineStr">
+        <is>
+          <t>shrestharakesh23@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG76" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH76" s="3" t="inlineStr"/>
+      <c r="AI76" s="3" t="inlineStr">
+        <is>
+          <t>02:14 hour</t>
+        </is>
+      </c>
+      <c r="AJ76" s="3" t="inlineStr"/>
+      <c r="AK76" s="3" t="inlineStr"/>
+      <c r="AL76" s="3" t="inlineStr">
+        <is>
+          <t>Sabina Baskota</t>
+        </is>
+      </c>
+      <c r="AM76" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AN76" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO76" s="3" t="inlineStr">
+        <is>
+          <t>L28-3</t>
+        </is>
+      </c>
+      <c r="AP76" s="3" t="inlineStr">
+        <is>
+          <t>85.360938</t>
+        </is>
+      </c>
+      <c r="AQ76" s="3" t="inlineStr"/>
+      <c r="AR76" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AS76" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT76" s="3" t="inlineStr">
+        <is>
+          <t>2h 13m</t>
+        </is>
+      </c>
+      <c r="AU76" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV76" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 Router  has been updated by Sanjeev Giri</t>
+        </is>
+      </c>
+      <c r="AW76" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX76" s="3" t="inlineStr">
+        <is>
+          <t>Sanjeev Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_29_Sep_2026.xlsx
@@ -15741,10 +15741,8 @@
           <t>Rakesh shrestha</t>
         </is>
       </c>
-      <c r="O76" s="3" t="inlineStr">
-        <is>
-          <t>9813632008</t>
-        </is>
+      <c r="O76" s="3" t="n">
+        <v>9813632008</v>
       </c>
       <c r="P76" s="3" t="inlineStr">
         <is>
@@ -15779,10 +15777,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y76" s="3" t="inlineStr">
-        <is>
-          <t>27.717205</t>
-        </is>
+      <c r="Y76" s="3" t="n">
+        <v>27.717205</v>
       </c>
       <c r="Z76" s="3" t="inlineStr">
         <is>
@@ -15838,25 +15834,21 @@
           <t>Sanjeev Giri</t>
         </is>
       </c>
-      <c r="AN76" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN76" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO76" s="3" t="inlineStr">
         <is>
           <t>L28-3</t>
         </is>
       </c>
-      <c r="AP76" s="3" t="inlineStr">
-        <is>
-          <t>85.360938</t>
-        </is>
+      <c r="AP76" s="3" t="n">
+        <v>85.360938</v>
       </c>
       <c r="AQ76" s="3" t="inlineStr"/>
       <c r="AR76" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6 Router  has been updated by Sanjeev Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS76" s="3" t="inlineStr">
